--- a/projects/project-3/assignment/src/data/ccom-qudt-structural-matches-with-defs.xlsx
+++ b/projects/project-3/assignment/src/data/ccom-qudt-structural-matches-with-defs.xlsx
@@ -610,7 +610,11 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -698,7 +702,11 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -830,7 +838,11 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1050,7 +1062,11 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1270,7 +1286,11 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1358,7 +1378,11 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1490,7 +1514,11 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1710,7 +1738,11 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1930,7 +1962,11 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2018,7 +2054,11 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2150,7 +2190,11 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2370,7 +2414,11 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2590,7 +2638,11 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2678,7 +2730,11 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2810,7 +2866,11 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3030,7 +3090,11 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3250,7 +3314,11 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3338,7 +3406,11 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3470,7 +3542,11 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3690,7 +3766,11 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3910,7 +3990,11 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3998,7 +4082,11 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4130,7 +4218,11 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4350,7 +4442,11 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4570,7 +4666,11 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4658,7 +4758,11 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4790,7 +4894,11 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5010,7 +5118,11 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5230,7 +5342,11 @@
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5318,7 +5434,11 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5450,7 +5570,11 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5670,7 +5794,11 @@
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5890,7 +6018,11 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5978,7 +6110,11 @@
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6110,7 +6246,11 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6330,7 +6470,11 @@
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6550,7 +6694,11 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6638,7 +6786,11 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6770,7 +6922,11 @@
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6990,7 +7146,11 @@
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7210,7 +7370,11 @@
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7298,7 +7462,11 @@
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7430,7 +7598,11 @@
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7650,7 +7822,11 @@
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7870,7 +8046,11 @@
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7958,7 +8138,11 @@
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8090,7 +8274,11 @@
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8310,7 +8498,11 @@
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -8530,7 +8722,11 @@
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8618,7 +8814,11 @@
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8750,7 +8950,11 @@
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8970,7 +9174,11 @@
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9190,7 +9398,11 @@
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -9278,7 +9490,11 @@
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -9410,7 +9626,11 @@
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -9630,7 +9850,11 @@
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
-      <c r="J209" t="inlineStr"/>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -9850,7 +10074,11 @@
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -9938,7 +10166,11 @@
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -10070,7 +10302,11 @@
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -10290,7 +10526,11 @@
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -10510,7 +10750,11 @@
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -10598,7 +10842,11 @@
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -10730,7 +10978,11 @@
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -10950,7 +11202,11 @@
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -11170,7 +11426,11 @@
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="J244" t="inlineStr"/>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -11258,7 +11518,11 @@
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -11390,7 +11654,11 @@
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
-      <c r="J249" t="inlineStr"/>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -11610,7 +11878,11 @@
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
-      <c r="J254" t="inlineStr"/>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -11830,7 +12102,11 @@
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
-      <c r="J259" t="inlineStr"/>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -11918,7 +12194,11 @@
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
-      <c r="J261" t="inlineStr"/>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -12050,7 +12330,11 @@
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
-      <c r="J264" t="inlineStr"/>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -12270,7 +12554,11 @@
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
-      <c r="J269" t="inlineStr"/>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -12490,7 +12778,11 @@
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -12578,7 +12870,11 @@
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -12710,7 +13006,11 @@
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -12930,7 +13230,11 @@
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
-      <c r="J284" t="inlineStr"/>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -13150,7 +13454,11 @@
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
-      <c r="J289" t="inlineStr"/>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -13238,7 +13546,11 @@
         </is>
       </c>
       <c r="I291" t="inlineStr"/>
-      <c r="J291" t="inlineStr"/>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -13370,7 +13682,11 @@
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
-      <c r="J294" t="inlineStr"/>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -13590,7 +13906,11 @@
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
-      <c r="J299" t="inlineStr"/>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -13810,7 +14130,11 @@
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
-      <c r="J304" t="inlineStr"/>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -13898,7 +14222,11 @@
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
-      <c r="J306" t="inlineStr"/>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -14030,7 +14358,11 @@
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
-      <c r="J309" t="inlineStr"/>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -14250,7 +14582,11 @@
         </is>
       </c>
       <c r="I314" t="inlineStr"/>
-      <c r="J314" t="inlineStr"/>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -14470,7 +14806,11 @@
         </is>
       </c>
       <c r="I319" t="inlineStr"/>
-      <c r="J319" t="inlineStr"/>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -14558,7 +14898,11 @@
         </is>
       </c>
       <c r="I321" t="inlineStr"/>
-      <c r="J321" t="inlineStr"/>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -14690,7 +15034,11 @@
         </is>
       </c>
       <c r="I324" t="inlineStr"/>
-      <c r="J324" t="inlineStr"/>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -14910,7 +15258,11 @@
         </is>
       </c>
       <c r="I329" t="inlineStr"/>
-      <c r="J329" t="inlineStr"/>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -15130,7 +15482,11 @@
         </is>
       </c>
       <c r="I334" t="inlineStr"/>
-      <c r="J334" t="inlineStr"/>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -15218,7 +15574,11 @@
         </is>
       </c>
       <c r="I336" t="inlineStr"/>
-      <c r="J336" t="inlineStr"/>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -15350,7 +15710,11 @@
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
-      <c r="J339" t="inlineStr"/>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -15570,7 +15934,11 @@
         </is>
       </c>
       <c r="I344" t="inlineStr"/>
-      <c r="J344" t="inlineStr"/>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -15790,7 +16158,11 @@
         </is>
       </c>
       <c r="I349" t="inlineStr"/>
-      <c r="J349" t="inlineStr"/>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -15878,7 +16250,11 @@
         </is>
       </c>
       <c r="I351" t="inlineStr"/>
-      <c r="J351" t="inlineStr"/>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -16010,7 +16386,11 @@
         </is>
       </c>
       <c r="I354" t="inlineStr"/>
-      <c r="J354" t="inlineStr"/>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -16230,7 +16610,11 @@
         </is>
       </c>
       <c r="I359" t="inlineStr"/>
-      <c r="J359" t="inlineStr"/>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -16450,7 +16834,11 @@
         </is>
       </c>
       <c r="I364" t="inlineStr"/>
-      <c r="J364" t="inlineStr"/>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -16538,7 +16926,11 @@
         </is>
       </c>
       <c r="I366" t="inlineStr"/>
-      <c r="J366" t="inlineStr"/>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -16670,7 +17062,11 @@
         </is>
       </c>
       <c r="I369" t="inlineStr"/>
-      <c r="J369" t="inlineStr"/>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -16890,7 +17286,11 @@
         </is>
       </c>
       <c r="I374" t="inlineStr"/>
-      <c r="J374" t="inlineStr"/>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -17110,7 +17510,11 @@
         </is>
       </c>
       <c r="I379" t="inlineStr"/>
-      <c r="J379" t="inlineStr"/>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -17198,7 +17602,11 @@
         </is>
       </c>
       <c r="I381" t="inlineStr"/>
-      <c r="J381" t="inlineStr"/>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -17330,7 +17738,11 @@
         </is>
       </c>
       <c r="I384" t="inlineStr"/>
-      <c r="J384" t="inlineStr"/>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -17550,7 +17962,11 @@
         </is>
       </c>
       <c r="I389" t="inlineStr"/>
-      <c r="J389" t="inlineStr"/>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -17770,7 +18186,11 @@
         </is>
       </c>
       <c r="I394" t="inlineStr"/>
-      <c r="J394" t="inlineStr"/>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -17858,7 +18278,11 @@
         </is>
       </c>
       <c r="I396" t="inlineStr"/>
-      <c r="J396" t="inlineStr"/>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -17990,7 +18414,11 @@
         </is>
       </c>
       <c r="I399" t="inlineStr"/>
-      <c r="J399" t="inlineStr"/>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -18210,7 +18638,11 @@
         </is>
       </c>
       <c r="I404" t="inlineStr"/>
-      <c r="J404" t="inlineStr"/>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -18430,7 +18862,11 @@
         </is>
       </c>
       <c r="I409" t="inlineStr"/>
-      <c r="J409" t="inlineStr"/>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -18518,7 +18954,11 @@
         </is>
       </c>
       <c r="I411" t="inlineStr"/>
-      <c r="J411" t="inlineStr"/>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -18650,7 +19090,11 @@
         </is>
       </c>
       <c r="I414" t="inlineStr"/>
-      <c r="J414" t="inlineStr"/>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -18870,7 +19314,11 @@
         </is>
       </c>
       <c r="I419" t="inlineStr"/>
-      <c r="J419" t="inlineStr"/>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -19090,7 +19538,11 @@
         </is>
       </c>
       <c r="I424" t="inlineStr"/>
-      <c r="J424" t="inlineStr"/>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -19178,7 +19630,11 @@
         </is>
       </c>
       <c r="I426" t="inlineStr"/>
-      <c r="J426" t="inlineStr"/>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -19310,7 +19766,11 @@
         </is>
       </c>
       <c r="I429" t="inlineStr"/>
-      <c r="J429" t="inlineStr"/>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -19530,7 +19990,11 @@
         </is>
       </c>
       <c r="I434" t="inlineStr"/>
-      <c r="J434" t="inlineStr"/>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -19750,7 +20214,11 @@
         </is>
       </c>
       <c r="I439" t="inlineStr"/>
-      <c r="J439" t="inlineStr"/>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -19838,7 +20306,11 @@
         </is>
       </c>
       <c r="I441" t="inlineStr"/>
-      <c r="J441" t="inlineStr"/>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -19970,7 +20442,11 @@
         </is>
       </c>
       <c r="I444" t="inlineStr"/>
-      <c r="J444" t="inlineStr"/>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -20190,7 +20666,11 @@
         </is>
       </c>
       <c r="I449" t="inlineStr"/>
-      <c r="J449" t="inlineStr"/>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -20410,7 +20890,11 @@
         </is>
       </c>
       <c r="I454" t="inlineStr"/>
-      <c r="J454" t="inlineStr"/>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -20498,7 +20982,11 @@
         </is>
       </c>
       <c r="I456" t="inlineStr"/>
-      <c r="J456" t="inlineStr"/>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -20630,7 +21118,11 @@
         </is>
       </c>
       <c r="I459" t="inlineStr"/>
-      <c r="J459" t="inlineStr"/>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -20850,7 +21342,11 @@
         </is>
       </c>
       <c r="I464" t="inlineStr"/>
-      <c r="J464" t="inlineStr"/>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -21070,7 +21566,11 @@
         </is>
       </c>
       <c r="I469" t="inlineStr"/>
-      <c r="J469" t="inlineStr"/>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -21158,7 +21658,11 @@
         </is>
       </c>
       <c r="I471" t="inlineStr"/>
-      <c r="J471" t="inlineStr"/>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -21290,7 +21794,11 @@
         </is>
       </c>
       <c r="I474" t="inlineStr"/>
-      <c r="J474" t="inlineStr"/>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -21510,7 +22018,11 @@
         </is>
       </c>
       <c r="I479" t="inlineStr"/>
-      <c r="J479" t="inlineStr"/>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -21730,7 +22242,11 @@
         </is>
       </c>
       <c r="I484" t="inlineStr"/>
-      <c r="J484" t="inlineStr"/>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -21818,7 +22334,11 @@
         </is>
       </c>
       <c r="I486" t="inlineStr"/>
-      <c r="J486" t="inlineStr"/>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -21950,7 +22470,11 @@
         </is>
       </c>
       <c r="I489" t="inlineStr"/>
-      <c r="J489" t="inlineStr"/>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -22170,7 +22694,11 @@
         </is>
       </c>
       <c r="I494" t="inlineStr"/>
-      <c r="J494" t="inlineStr"/>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -22390,7 +22918,11 @@
         </is>
       </c>
       <c r="I499" t="inlineStr"/>
-      <c r="J499" t="inlineStr"/>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -22478,7 +23010,11 @@
         </is>
       </c>
       <c r="I501" t="inlineStr"/>
-      <c r="J501" t="inlineStr"/>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -22610,7 +23146,11 @@
         </is>
       </c>
       <c r="I504" t="inlineStr"/>
-      <c r="J504" t="inlineStr"/>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -22830,7 +23370,11 @@
         </is>
       </c>
       <c r="I509" t="inlineStr"/>
-      <c r="J509" t="inlineStr"/>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -23050,7 +23594,11 @@
         </is>
       </c>
       <c r="I514" t="inlineStr"/>
-      <c r="J514" t="inlineStr"/>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -23138,7 +23686,11 @@
         </is>
       </c>
       <c r="I516" t="inlineStr"/>
-      <c r="J516" t="inlineStr"/>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -23270,7 +23822,11 @@
         </is>
       </c>
       <c r="I519" t="inlineStr"/>
-      <c r="J519" t="inlineStr"/>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -23490,7 +24046,11 @@
         </is>
       </c>
       <c r="I524" t="inlineStr"/>
-      <c r="J524" t="inlineStr"/>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -23710,7 +24270,11 @@
         </is>
       </c>
       <c r="I529" t="inlineStr"/>
-      <c r="J529" t="inlineStr"/>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -23798,7 +24362,11 @@
         </is>
       </c>
       <c r="I531" t="inlineStr"/>
-      <c r="J531" t="inlineStr"/>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -23930,7 +24498,11 @@
         </is>
       </c>
       <c r="I534" t="inlineStr"/>
-      <c r="J534" t="inlineStr"/>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -24150,7 +24722,11 @@
         </is>
       </c>
       <c r="I539" t="inlineStr"/>
-      <c r="J539" t="inlineStr"/>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -24370,7 +24946,11 @@
         </is>
       </c>
       <c r="I544" t="inlineStr"/>
-      <c r="J544" t="inlineStr"/>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -24458,7 +25038,11 @@
         </is>
       </c>
       <c r="I546" t="inlineStr"/>
-      <c r="J546" t="inlineStr"/>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -24590,7 +25174,11 @@
         </is>
       </c>
       <c r="I549" t="inlineStr"/>
-      <c r="J549" t="inlineStr"/>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -24810,7 +25398,11 @@
         </is>
       </c>
       <c r="I554" t="inlineStr"/>
-      <c r="J554" t="inlineStr"/>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -25030,7 +25622,11 @@
         </is>
       </c>
       <c r="I559" t="inlineStr"/>
-      <c r="J559" t="inlineStr"/>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -25118,7 +25714,11 @@
         </is>
       </c>
       <c r="I561" t="inlineStr"/>
-      <c r="J561" t="inlineStr"/>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -25250,7 +25850,11 @@
         </is>
       </c>
       <c r="I564" t="inlineStr"/>
-      <c r="J564" t="inlineStr"/>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -25470,7 +26074,11 @@
         </is>
       </c>
       <c r="I569" t="inlineStr"/>
-      <c r="J569" t="inlineStr"/>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -25690,7 +26298,11 @@
         </is>
       </c>
       <c r="I574" t="inlineStr"/>
-      <c r="J574" t="inlineStr"/>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -25778,7 +26390,11 @@
         </is>
       </c>
       <c r="I576" t="inlineStr"/>
-      <c r="J576" t="inlineStr"/>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -25910,7 +26526,11 @@
         </is>
       </c>
       <c r="I579" t="inlineStr"/>
-      <c r="J579" t="inlineStr"/>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -26130,7 +26750,11 @@
         </is>
       </c>
       <c r="I584" t="inlineStr"/>
-      <c r="J584" t="inlineStr"/>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -26350,7 +26974,11 @@
         </is>
       </c>
       <c r="I589" t="inlineStr"/>
-      <c r="J589" t="inlineStr"/>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -26438,7 +27066,11 @@
         </is>
       </c>
       <c r="I591" t="inlineStr"/>
-      <c r="J591" t="inlineStr"/>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -26570,7 +27202,11 @@
         </is>
       </c>
       <c r="I594" t="inlineStr"/>
-      <c r="J594" t="inlineStr"/>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -26790,7 +27426,11 @@
         </is>
       </c>
       <c r="I599" t="inlineStr"/>
-      <c r="J599" t="inlineStr"/>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -27010,7 +27650,11 @@
         </is>
       </c>
       <c r="I604" t="inlineStr"/>
-      <c r="J604" t="inlineStr"/>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -27098,7 +27742,11 @@
         </is>
       </c>
       <c r="I606" t="inlineStr"/>
-      <c r="J606" t="inlineStr"/>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -27230,7 +27878,11 @@
         </is>
       </c>
       <c r="I609" t="inlineStr"/>
-      <c r="J609" t="inlineStr"/>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -27450,7 +28102,11 @@
         </is>
       </c>
       <c r="I614" t="inlineStr"/>
-      <c r="J614" t="inlineStr"/>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -27670,7 +28326,11 @@
         </is>
       </c>
       <c r="I619" t="inlineStr"/>
-      <c r="J619" t="inlineStr"/>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -27758,7 +28418,11 @@
         </is>
       </c>
       <c r="I621" t="inlineStr"/>
-      <c r="J621" t="inlineStr"/>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -27890,7 +28554,11 @@
         </is>
       </c>
       <c r="I624" t="inlineStr"/>
-      <c r="J624" t="inlineStr"/>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -28110,7 +28778,11 @@
         </is>
       </c>
       <c r="I629" t="inlineStr"/>
-      <c r="J629" t="inlineStr"/>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -28330,7 +29002,11 @@
         </is>
       </c>
       <c r="I634" t="inlineStr"/>
-      <c r="J634" t="inlineStr"/>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -28418,7 +29094,11 @@
         </is>
       </c>
       <c r="I636" t="inlineStr"/>
-      <c r="J636" t="inlineStr"/>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -28550,7 +29230,11 @@
         </is>
       </c>
       <c r="I639" t="inlineStr"/>
-      <c r="J639" t="inlineStr"/>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -28770,7 +29454,11 @@
         </is>
       </c>
       <c r="I644" t="inlineStr"/>
-      <c r="J644" t="inlineStr"/>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">

--- a/projects/project-3/assignment/src/data/ccom-qudt-structural-matches-with-defs.xlsx
+++ b/projects/project-3/assignment/src/data/ccom-qudt-structural-matches-with-defs.xlsx
@@ -521,7 +521,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Years and spans at least one Year.</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -565,7 +569,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Years and spans at least one Year.</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -609,7 +617,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Years and spans at least one Year.</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -657,7 +669,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Years and spans at least one Year.</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -701,7 +717,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Years and spans at least one Year.</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -749,7 +769,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Years and spans at least one Year.</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -793,7 +817,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Years and spans at least one Year.</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -837,7 +865,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Years and spans at least one Year.</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -885,7 +917,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Years and spans at least one Year.</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -929,7 +965,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Years and spans at least one Year.</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -973,7 +1013,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Years and spans at least one Year.</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1017,7 +1061,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Years and spans at least one Year.</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1061,7 +1109,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Years and spans at least one Year.</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -1109,7 +1161,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Years and spans at least one Year.</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1153,7 +1209,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Years and spans at least one Year.</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1197,7 +1257,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that describes some Entity.</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1241,7 +1305,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that describes some Entity.</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1285,7 +1353,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that describes some Entity.</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -1333,7 +1405,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that describes some Entity.</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1377,7 +1453,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that describes some Entity.</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -1425,7 +1505,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that describes some Entity.</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1469,7 +1553,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that describes some Entity.</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1513,7 +1601,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that describes some Entity.</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -1561,7 +1653,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that describes some Entity.</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1605,7 +1701,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that describes some Entity.</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1649,7 +1749,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that describes some Entity.</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -1693,7 +1797,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that describes some Entity.</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1737,7 +1845,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that describes some Entity.</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -1785,7 +1897,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that describes some Entity.</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1829,7 +1945,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that describes some Entity.</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -1873,7 +1993,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>A Decimal Time of Day Identifier that designates a Julian Date and is composed of both a Julian Day Number and a Julian Date Fraction.</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1917,7 +2041,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>A Decimal Time of Day Identifier that designates a Julian Date and is composed of both a Julian Day Number and a Julian Date Fraction.</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
@@ -1961,7 +2089,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>A Decimal Time of Day Identifier that designates a Julian Date and is composed of both a Julian Day Number and a Julian Date Fraction.</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -2009,7 +2141,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>A Decimal Time of Day Identifier that designates a Julian Date and is composed of both a Julian Day Number and a Julian Date Fraction.</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -2053,7 +2189,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>A Decimal Time of Day Identifier that designates a Julian Date and is composed of both a Julian Day Number and a Julian Date Fraction.</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -2101,7 +2241,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>A Decimal Time of Day Identifier that designates a Julian Date and is composed of both a Julian Day Number and a Julian Date Fraction.</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -2145,7 +2289,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>A Decimal Time of Day Identifier that designates a Julian Date and is composed of both a Julian Day Number and a Julian Date Fraction.</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -2189,7 +2337,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>A Decimal Time of Day Identifier that designates a Julian Date and is composed of both a Julian Day Number and a Julian Date Fraction.</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -2237,7 +2389,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>A Decimal Time of Day Identifier that designates a Julian Date and is composed of both a Julian Day Number and a Julian Date Fraction.</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
@@ -2281,7 +2437,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>A Decimal Time of Day Identifier that designates a Julian Date and is composed of both a Julian Day Number and a Julian Date Fraction.</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -2325,7 +2485,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>A Decimal Time of Day Identifier that designates a Julian Date and is composed of both a Julian Day Number and a Julian Date Fraction.</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -2369,7 +2533,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>A Decimal Time of Day Identifier that designates a Julian Date and is composed of both a Julian Day Number and a Julian Date Fraction.</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -2413,7 +2581,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>A Decimal Time of Day Identifier that designates a Julian Date and is composed of both a Julian Day Number and a Julian Date Fraction.</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -2461,7 +2633,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>A Decimal Time of Day Identifier that designates a Julian Date and is composed of both a Julian Day Number and a Julian Date Fraction.</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -2505,7 +2681,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>A Decimal Time of Day Identifier that designates a Julian Date and is composed of both a Julian Day Number and a Julian Date Fraction.</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -2549,7 +2729,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one Orbital Revolution around its Primary Body as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -2593,7 +2777,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one Orbital Revolution around its Primary Body as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -2637,7 +2825,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one Orbital Revolution around its Primary Body as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -2685,7 +2877,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one Orbital Revolution around its Primary Body as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
@@ -2729,7 +2925,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one Orbital Revolution around its Primary Body as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -2777,7 +2977,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one Orbital Revolution around its Primary Body as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -2821,7 +3025,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one Orbital Revolution around its Primary Body as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -2865,7 +3073,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one Orbital Revolution around its Primary Body as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -2913,7 +3125,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one Orbital Revolution around its Primary Body as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -2957,7 +3173,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one Orbital Revolution around its Primary Body as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -3001,7 +3221,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one Orbital Revolution around its Primary Body as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -3045,7 +3269,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one Orbital Revolution around its Primary Body as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
@@ -3089,7 +3317,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one Orbital Revolution around its Primary Body as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -3137,7 +3369,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one Orbital Revolution around its Primary Body as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -3181,7 +3417,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one Orbital Revolution around its Primary Body as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
@@ -3225,7 +3465,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that places a Quality of an Entity onto some interval scale having no true zero value.</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -3269,7 +3513,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that places a Quality of an Entity onto some interval scale having no true zero value.</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
@@ -3313,7 +3561,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that places a Quality of an Entity onto some interval scale having no true zero value.</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -3361,7 +3613,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that places a Quality of an Entity onto some interval scale having no true zero value.</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
@@ -3405,7 +3661,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that places a Quality of an Entity onto some interval scale having no true zero value.</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -3453,7 +3713,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that places a Quality of an Entity onto some interval scale having no true zero value.</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
@@ -3497,7 +3761,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that places a Quality of an Entity onto some interval scale having no true zero value.</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
@@ -3541,7 +3809,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that places a Quality of an Entity onto some interval scale having no true zero value.</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -3589,7 +3861,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that places a Quality of an Entity onto some interval scale having no true zero value.</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
@@ -3633,7 +3909,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that places a Quality of an Entity onto some interval scale having no true zero value.</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr"/>
     </row>
     <row r="72">
@@ -3677,7 +3957,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that places a Quality of an Entity onto some interval scale having no true zero value.</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr"/>
     </row>
     <row r="73">
@@ -3721,7 +4005,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that places a Quality of an Entity onto some interval scale having no true zero value.</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
@@ -3765,7 +4053,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that places a Quality of an Entity onto some interval scale having no true zero value.</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -3813,7 +4105,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that places a Quality of an Entity onto some interval scale having no true zero value.</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr"/>
     </row>
     <row r="76">
@@ -3857,7 +4153,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that places a Quality of an Entity onto some interval scale having no true zero value.</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr"/>
     </row>
     <row r="77">
@@ -3901,7 +4201,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>A Temporal Instant Identifier that designates some Time of Day.</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
@@ -3945,7 +4249,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>A Temporal Instant Identifier that designates some Time of Day.</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr"/>
     </row>
     <row r="79">
@@ -3989,7 +4297,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>A Temporal Instant Identifier that designates some Time of Day.</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -4037,7 +4349,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>A Temporal Instant Identifier that designates some Time of Day.</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr"/>
     </row>
     <row r="81">
@@ -4081,7 +4397,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>A Temporal Instant Identifier that designates some Time of Day.</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -4129,7 +4449,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>A Temporal Instant Identifier that designates some Time of Day.</t>
+        </is>
+      </c>
       <c r="J82" t="inlineStr"/>
     </row>
     <row r="83">
@@ -4173,7 +4497,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>A Temporal Instant Identifier that designates some Time of Day.</t>
+        </is>
+      </c>
       <c r="J83" t="inlineStr"/>
     </row>
     <row r="84">
@@ -4217,7 +4545,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>A Temporal Instant Identifier that designates some Time of Day.</t>
+        </is>
+      </c>
       <c r="J84" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -4265,7 +4597,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>A Temporal Instant Identifier that designates some Time of Day.</t>
+        </is>
+      </c>
       <c r="J85" t="inlineStr"/>
     </row>
     <row r="86">
@@ -4309,7 +4645,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>A Temporal Instant Identifier that designates some Time of Day.</t>
+        </is>
+      </c>
       <c r="J86" t="inlineStr"/>
     </row>
     <row r="87">
@@ -4353,7 +4693,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>A Temporal Instant Identifier that designates some Time of Day.</t>
+        </is>
+      </c>
       <c r="J87" t="inlineStr"/>
     </row>
     <row r="88">
@@ -4397,7 +4741,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>A Temporal Instant Identifier that designates some Time of Day.</t>
+        </is>
+      </c>
       <c r="J88" t="inlineStr"/>
     </row>
     <row r="89">
@@ -4441,7 +4789,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>A Temporal Instant Identifier that designates some Time of Day.</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -4489,7 +4841,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>A Temporal Instant Identifier that designates some Time of Day.</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr"/>
     </row>
     <row r="91">
@@ -4533,7 +4889,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>A Temporal Instant Identifier that designates some Time of Day.</t>
+        </is>
+      </c>
       <c r="J91" t="inlineStr"/>
     </row>
     <row r="92">
@@ -4577,7 +4937,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>A Geospatial Position that is a proper part of some Geospatial Region Bounding Box.</t>
+        </is>
+      </c>
       <c r="J92" t="inlineStr"/>
     </row>
     <row r="93">
@@ -4621,7 +4985,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>A Geospatial Position that is a proper part of some Geospatial Region Bounding Box.</t>
+        </is>
+      </c>
       <c r="J93" t="inlineStr"/>
     </row>
     <row r="94">
@@ -4665,7 +5033,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>A Geospatial Position that is a proper part of some Geospatial Region Bounding Box.</t>
+        </is>
+      </c>
       <c r="J94" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -4713,7 +5085,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>A Geospatial Position that is a proper part of some Geospatial Region Bounding Box.</t>
+        </is>
+      </c>
       <c r="J95" t="inlineStr"/>
     </row>
     <row r="96">
@@ -4757,7 +5133,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>A Geospatial Position that is a proper part of some Geospatial Region Bounding Box.</t>
+        </is>
+      </c>
       <c r="J96" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -4805,7 +5185,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>A Geospatial Position that is a proper part of some Geospatial Region Bounding Box.</t>
+        </is>
+      </c>
       <c r="J97" t="inlineStr"/>
     </row>
     <row r="98">
@@ -4849,7 +5233,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>A Geospatial Position that is a proper part of some Geospatial Region Bounding Box.</t>
+        </is>
+      </c>
       <c r="J98" t="inlineStr"/>
     </row>
     <row r="99">
@@ -4893,7 +5281,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>A Geospatial Position that is a proper part of some Geospatial Region Bounding Box.</t>
+        </is>
+      </c>
       <c r="J99" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -4941,7 +5333,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>A Geospatial Position that is a proper part of some Geospatial Region Bounding Box.</t>
+        </is>
+      </c>
       <c r="J100" t="inlineStr"/>
     </row>
     <row r="101">
@@ -4985,7 +5381,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>A Geospatial Position that is a proper part of some Geospatial Region Bounding Box.</t>
+        </is>
+      </c>
       <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
@@ -5029,7 +5429,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>A Geospatial Position that is a proper part of some Geospatial Region Bounding Box.</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr"/>
     </row>
     <row r="103">
@@ -5073,7 +5477,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>A Geospatial Position that is a proper part of some Geospatial Region Bounding Box.</t>
+        </is>
+      </c>
       <c r="J103" t="inlineStr"/>
     </row>
     <row r="104">
@@ -5117,7 +5525,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>A Geospatial Position that is a proper part of some Geospatial Region Bounding Box.</t>
+        </is>
+      </c>
       <c r="J104" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -5165,7 +5577,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>A Geospatial Position that is a proper part of some Geospatial Region Bounding Box.</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr"/>
     </row>
     <row r="106">
@@ -5209,7 +5625,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>A Geospatial Position that is a proper part of some Geospatial Region Bounding Box.</t>
+        </is>
+      </c>
       <c r="J106" t="inlineStr"/>
     </row>
     <row r="107">
@@ -5253,7 +5673,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places an Entity into some rank order.</t>
+        </is>
+      </c>
       <c r="J107" t="inlineStr"/>
     </row>
     <row r="108">
@@ -5297,7 +5721,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places an Entity into some rank order.</t>
+        </is>
+      </c>
       <c r="J108" t="inlineStr"/>
     </row>
     <row r="109">
@@ -5341,7 +5769,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places an Entity into some rank order.</t>
+        </is>
+      </c>
       <c r="J109" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -5389,7 +5821,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places an Entity into some rank order.</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
     </row>
     <row r="111">
@@ -5433,7 +5869,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places an Entity into some rank order.</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -5481,7 +5921,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places an Entity into some rank order.</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr"/>
     </row>
     <row r="113">
@@ -5525,7 +5969,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places an Entity into some rank order.</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
     </row>
     <row r="114">
@@ -5569,7 +6017,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places an Entity into some rank order.</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -5617,7 +6069,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places an Entity into some rank order.</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
     </row>
     <row r="116">
@@ -5661,7 +6117,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places an Entity into some rank order.</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr"/>
     </row>
     <row r="117">
@@ -5705,7 +6165,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places an Entity into some rank order.</t>
+        </is>
+      </c>
       <c r="J117" t="inlineStr"/>
     </row>
     <row r="118">
@@ -5749,7 +6213,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places an Entity into some rank order.</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr"/>
     </row>
     <row r="119">
@@ -5793,7 +6261,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places an Entity into some rank order.</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -5841,7 +6313,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places an Entity into some rank order.</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr"/>
     </row>
     <row r="121">
@@ -5885,7 +6361,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places an Entity into some rank order.</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr"/>
     </row>
     <row r="122">
@@ -5929,7 +6409,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Weeks and spans at least one Week.</t>
+        </is>
+      </c>
       <c r="J122" t="inlineStr"/>
     </row>
     <row r="123">
@@ -5973,7 +6457,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Weeks and spans at least one Week.</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
     </row>
     <row r="124">
@@ -6017,7 +6505,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Weeks and spans at least one Week.</t>
+        </is>
+      </c>
       <c r="J124" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -6065,7 +6557,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Weeks and spans at least one Week.</t>
+        </is>
+      </c>
       <c r="J125" t="inlineStr"/>
     </row>
     <row r="126">
@@ -6109,7 +6605,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Weeks and spans at least one Week.</t>
+        </is>
+      </c>
       <c r="J126" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -6157,7 +6657,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Weeks and spans at least one Week.</t>
+        </is>
+      </c>
       <c r="J127" t="inlineStr"/>
     </row>
     <row r="128">
@@ -6201,7 +6705,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Weeks and spans at least one Week.</t>
+        </is>
+      </c>
       <c r="J128" t="inlineStr"/>
     </row>
     <row r="129">
@@ -6245,7 +6753,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Weeks and spans at least one Week.</t>
+        </is>
+      </c>
       <c r="J129" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -6293,7 +6805,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Weeks and spans at least one Week.</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr"/>
     </row>
     <row r="131">
@@ -6337,7 +6853,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Weeks and spans at least one Week.</t>
+        </is>
+      </c>
       <c r="J131" t="inlineStr"/>
     </row>
     <row r="132">
@@ -6381,7 +6901,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Weeks and spans at least one Week.</t>
+        </is>
+      </c>
       <c r="J132" t="inlineStr"/>
     </row>
     <row r="133">
@@ -6425,7 +6949,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Weeks and spans at least one Week.</t>
+        </is>
+      </c>
       <c r="J133" t="inlineStr"/>
     </row>
     <row r="134">
@@ -6469,7 +6997,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Weeks and spans at least one Week.</t>
+        </is>
+      </c>
       <c r="J134" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -6517,7 +7049,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Weeks and spans at least one Week.</t>
+        </is>
+      </c>
       <c r="J135" t="inlineStr"/>
     </row>
     <row r="136">
@@ -6561,7 +7097,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Weeks and spans at least one Week.</t>
+        </is>
+      </c>
       <c r="J136" t="inlineStr"/>
     </row>
     <row r="137">
@@ -6605,7 +7145,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that consists of a set of symbols that designate some Entity.</t>
+        </is>
+      </c>
       <c r="J137" t="inlineStr"/>
     </row>
     <row r="138">
@@ -6649,7 +7193,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that consists of a set of symbols that designate some Entity.</t>
+        </is>
+      </c>
       <c r="J138" t="inlineStr"/>
     </row>
     <row r="139">
@@ -6693,7 +7241,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that consists of a set of symbols that designate some Entity.</t>
+        </is>
+      </c>
       <c r="J139" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -6741,7 +7293,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that consists of a set of symbols that designate some Entity.</t>
+        </is>
+      </c>
       <c r="J140" t="inlineStr"/>
     </row>
     <row r="141">
@@ -6785,7 +7341,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that consists of a set of symbols that designate some Entity.</t>
+        </is>
+      </c>
       <c r="J141" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -6833,7 +7393,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that consists of a set of symbols that designate some Entity.</t>
+        </is>
+      </c>
       <c r="J142" t="inlineStr"/>
     </row>
     <row r="143">
@@ -6877,7 +7441,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that consists of a set of symbols that designate some Entity.</t>
+        </is>
+      </c>
       <c r="J143" t="inlineStr"/>
     </row>
     <row r="144">
@@ -6921,7 +7489,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that consists of a set of symbols that designate some Entity.</t>
+        </is>
+      </c>
       <c r="J144" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -6969,7 +7541,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that consists of a set of symbols that designate some Entity.</t>
+        </is>
+      </c>
       <c r="J145" t="inlineStr"/>
     </row>
     <row r="146">
@@ -7013,7 +7589,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that consists of a set of symbols that designate some Entity.</t>
+        </is>
+      </c>
       <c r="J146" t="inlineStr"/>
     </row>
     <row r="147">
@@ -7057,7 +7637,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that consists of a set of symbols that designate some Entity.</t>
+        </is>
+      </c>
       <c r="J147" t="inlineStr"/>
     </row>
     <row r="148">
@@ -7101,7 +7685,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that consists of a set of symbols that designate some Entity.</t>
+        </is>
+      </c>
       <c r="J148" t="inlineStr"/>
     </row>
     <row r="149">
@@ -7145,7 +7733,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that consists of a set of symbols that designate some Entity.</t>
+        </is>
+      </c>
       <c r="J149" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -7193,7 +7785,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that consists of a set of symbols that designate some Entity.</t>
+        </is>
+      </c>
       <c r="J150" t="inlineStr"/>
     </row>
     <row r="151">
@@ -7237,7 +7833,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that consists of a set of symbols that designate some Entity.</t>
+        </is>
+      </c>
       <c r="J151" t="inlineStr"/>
     </row>
     <row r="152">
@@ -7281,7 +7881,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Interval.</t>
+        </is>
+      </c>
       <c r="J152" t="inlineStr"/>
     </row>
     <row r="153">
@@ -7325,7 +7929,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Interval.</t>
+        </is>
+      </c>
       <c r="J153" t="inlineStr"/>
     </row>
     <row r="154">
@@ -7369,7 +7977,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Interval.</t>
+        </is>
+      </c>
       <c r="J154" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -7417,7 +8029,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Interval.</t>
+        </is>
+      </c>
       <c r="J155" t="inlineStr"/>
     </row>
     <row r="156">
@@ -7461,7 +8077,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Interval.</t>
+        </is>
+      </c>
       <c r="J156" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -7509,7 +8129,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Interval.</t>
+        </is>
+      </c>
       <c r="J157" t="inlineStr"/>
     </row>
     <row r="158">
@@ -7553,7 +8177,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Interval.</t>
+        </is>
+      </c>
       <c r="J158" t="inlineStr"/>
     </row>
     <row r="159">
@@ -7597,7 +8225,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Interval.</t>
+        </is>
+      </c>
       <c r="J159" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -7645,7 +8277,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Interval.</t>
+        </is>
+      </c>
       <c r="J160" t="inlineStr"/>
     </row>
     <row r="161">
@@ -7689,7 +8325,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Interval.</t>
+        </is>
+      </c>
       <c r="J161" t="inlineStr"/>
     </row>
     <row r="162">
@@ -7733,7 +8373,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Interval.</t>
+        </is>
+      </c>
       <c r="J162" t="inlineStr"/>
     </row>
     <row r="163">
@@ -7777,7 +8421,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Interval.</t>
+        </is>
+      </c>
       <c r="J163" t="inlineStr"/>
     </row>
     <row r="164">
@@ -7821,7 +8469,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Interval.</t>
+        </is>
+      </c>
       <c r="J164" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -7869,7 +8521,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Interval.</t>
+        </is>
+      </c>
       <c r="J165" t="inlineStr"/>
     </row>
     <row r="166">
@@ -7913,7 +8569,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Interval.</t>
+        </is>
+      </c>
       <c r="J166" t="inlineStr"/>
     </row>
     <row r="167">
@@ -7957,7 +8617,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr"/>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places a Quality of an Entity onto an interval scale having a true zero value.</t>
+        </is>
+      </c>
       <c r="J167" t="inlineStr"/>
     </row>
     <row r="168">
@@ -8001,7 +8665,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr"/>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places a Quality of an Entity onto an interval scale having a true zero value.</t>
+        </is>
+      </c>
       <c r="J168" t="inlineStr"/>
     </row>
     <row r="169">
@@ -8045,7 +8713,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places a Quality of an Entity onto an interval scale having a true zero value.</t>
+        </is>
+      </c>
       <c r="J169" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -8093,7 +8765,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr"/>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places a Quality of an Entity onto an interval scale having a true zero value.</t>
+        </is>
+      </c>
       <c r="J170" t="inlineStr"/>
     </row>
     <row r="171">
@@ -8137,7 +8813,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places a Quality of an Entity onto an interval scale having a true zero value.</t>
+        </is>
+      </c>
       <c r="J171" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -8185,7 +8865,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places a Quality of an Entity onto an interval scale having a true zero value.</t>
+        </is>
+      </c>
       <c r="J172" t="inlineStr"/>
     </row>
     <row r="173">
@@ -8229,7 +8913,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr"/>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places a Quality of an Entity onto an interval scale having a true zero value.</t>
+        </is>
+      </c>
       <c r="J173" t="inlineStr"/>
     </row>
     <row r="174">
@@ -8273,7 +8961,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr"/>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places a Quality of an Entity onto an interval scale having a true zero value.</t>
+        </is>
+      </c>
       <c r="J174" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -8321,7 +9013,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr"/>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places a Quality of an Entity onto an interval scale having a true zero value.</t>
+        </is>
+      </c>
       <c r="J175" t="inlineStr"/>
     </row>
     <row r="176">
@@ -8365,7 +9061,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places a Quality of an Entity onto an interval scale having a true zero value.</t>
+        </is>
+      </c>
       <c r="J176" t="inlineStr"/>
     </row>
     <row r="177">
@@ -8409,7 +9109,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places a Quality of an Entity onto an interval scale having a true zero value.</t>
+        </is>
+      </c>
       <c r="J177" t="inlineStr"/>
     </row>
     <row r="178">
@@ -8453,7 +9157,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places a Quality of an Entity onto an interval scale having a true zero value.</t>
+        </is>
+      </c>
       <c r="J178" t="inlineStr"/>
     </row>
     <row r="179">
@@ -8497,7 +9205,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr"/>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places a Quality of an Entity onto an interval scale having a true zero value.</t>
+        </is>
+      </c>
       <c r="J179" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -8545,7 +9257,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places a Quality of an Entity onto an interval scale having a true zero value.</t>
+        </is>
+      </c>
       <c r="J180" t="inlineStr"/>
     </row>
     <row r="181">
@@ -8589,7 +9305,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that places a Quality of an Entity onto an interval scale having a true zero value.</t>
+        </is>
+      </c>
       <c r="J181" t="inlineStr"/>
     </row>
     <row r="182">
@@ -8633,7 +9353,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>A One-Dimensional Spatial Region that consists of the idealized line along which an Object has traversed during some motion.</t>
+        </is>
+      </c>
       <c r="J182" t="inlineStr"/>
     </row>
     <row r="183">
@@ -8677,7 +9401,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>A One-Dimensional Spatial Region that consists of the idealized line along which an Object has traversed during some motion.</t>
+        </is>
+      </c>
       <c r="J183" t="inlineStr"/>
     </row>
     <row r="184">
@@ -8721,7 +9449,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>A One-Dimensional Spatial Region that consists of the idealized line along which an Object has traversed during some motion.</t>
+        </is>
+      </c>
       <c r="J184" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -8769,7 +9501,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr"/>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>A One-Dimensional Spatial Region that consists of the idealized line along which an Object has traversed during some motion.</t>
+        </is>
+      </c>
       <c r="J185" t="inlineStr"/>
     </row>
     <row r="186">
@@ -8813,7 +9549,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr"/>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>A One-Dimensional Spatial Region that consists of the idealized line along which an Object has traversed during some motion.</t>
+        </is>
+      </c>
       <c r="J186" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -8861,7 +9601,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr"/>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>A One-Dimensional Spatial Region that consists of the idealized line along which an Object has traversed during some motion.</t>
+        </is>
+      </c>
       <c r="J187" t="inlineStr"/>
     </row>
     <row r="188">
@@ -8905,7 +9649,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr"/>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>A One-Dimensional Spatial Region that consists of the idealized line along which an Object has traversed during some motion.</t>
+        </is>
+      </c>
       <c r="J188" t="inlineStr"/>
     </row>
     <row r="189">
@@ -8949,7 +9697,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr"/>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>A One-Dimensional Spatial Region that consists of the idealized line along which an Object has traversed during some motion.</t>
+        </is>
+      </c>
       <c r="J189" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -8997,7 +9749,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr"/>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>A One-Dimensional Spatial Region that consists of the idealized line along which an Object has traversed during some motion.</t>
+        </is>
+      </c>
       <c r="J190" t="inlineStr"/>
     </row>
     <row r="191">
@@ -9041,7 +9797,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr"/>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>A One-Dimensional Spatial Region that consists of the idealized line along which an Object has traversed during some motion.</t>
+        </is>
+      </c>
       <c r="J191" t="inlineStr"/>
     </row>
     <row r="192">
@@ -9085,7 +9845,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>A One-Dimensional Spatial Region that consists of the idealized line along which an Object has traversed during some motion.</t>
+        </is>
+      </c>
       <c r="J192" t="inlineStr"/>
     </row>
     <row r="193">
@@ -9129,7 +9893,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>A One-Dimensional Spatial Region that consists of the idealized line along which an Object has traversed during some motion.</t>
+        </is>
+      </c>
       <c r="J193" t="inlineStr"/>
     </row>
     <row r="194">
@@ -9173,7 +9941,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>A One-Dimensional Spatial Region that consists of the idealized line along which an Object has traversed during some motion.</t>
+        </is>
+      </c>
       <c r="J194" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -9221,7 +9993,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr"/>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>A One-Dimensional Spatial Region that consists of the idealized line along which an Object has traversed during some motion.</t>
+        </is>
+      </c>
       <c r="J195" t="inlineStr"/>
     </row>
     <row r="196">
@@ -9265,7 +10041,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>A One-Dimensional Spatial Region that consists of the idealized line along which an Object has traversed during some motion.</t>
+        </is>
+      </c>
       <c r="J196" t="inlineStr"/>
     </row>
     <row r="197">
@@ -9309,7 +10089,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the duration of 9,192,631,770 periods of the radiation corresponding to the transition between the two hyperfine levels of the ground state of the cesium 133 atom.</t>
+        </is>
+      </c>
       <c r="J197" t="inlineStr"/>
     </row>
     <row r="198">
@@ -9353,7 +10137,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the duration of 9,192,631,770 periods of the radiation corresponding to the transition between the two hyperfine levels of the ground state of the cesium 133 atom.</t>
+        </is>
+      </c>
       <c r="J198" t="inlineStr"/>
     </row>
     <row r="199">
@@ -9397,7 +10185,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the duration of 9,192,631,770 periods of the radiation corresponding to the transition between the two hyperfine levels of the ground state of the cesium 133 atom.</t>
+        </is>
+      </c>
       <c r="J199" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -9445,7 +10237,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the duration of 9,192,631,770 periods of the radiation corresponding to the transition between the two hyperfine levels of the ground state of the cesium 133 atom.</t>
+        </is>
+      </c>
       <c r="J200" t="inlineStr"/>
     </row>
     <row r="201">
@@ -9489,7 +10285,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr"/>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the duration of 9,192,631,770 periods of the radiation corresponding to the transition between the two hyperfine levels of the ground state of the cesium 133 atom.</t>
+        </is>
+      </c>
       <c r="J201" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -9537,7 +10337,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr"/>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the duration of 9,192,631,770 periods of the radiation corresponding to the transition between the two hyperfine levels of the ground state of the cesium 133 atom.</t>
+        </is>
+      </c>
       <c r="J202" t="inlineStr"/>
     </row>
     <row r="203">
@@ -9581,7 +10385,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr"/>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the duration of 9,192,631,770 periods of the radiation corresponding to the transition between the two hyperfine levels of the ground state of the cesium 133 atom.</t>
+        </is>
+      </c>
       <c r="J203" t="inlineStr"/>
     </row>
     <row r="204">
@@ -9625,7 +10433,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr"/>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the duration of 9,192,631,770 periods of the radiation corresponding to the transition between the two hyperfine levels of the ground state of the cesium 133 atom.</t>
+        </is>
+      </c>
       <c r="J204" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -9673,7 +10485,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr"/>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the duration of 9,192,631,770 periods of the radiation corresponding to the transition between the two hyperfine levels of the ground state of the cesium 133 atom.</t>
+        </is>
+      </c>
       <c r="J205" t="inlineStr"/>
     </row>
     <row r="206">
@@ -9717,7 +10533,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr"/>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the duration of 9,192,631,770 periods of the radiation corresponding to the transition between the two hyperfine levels of the ground state of the cesium 133 atom.</t>
+        </is>
+      </c>
       <c r="J206" t="inlineStr"/>
     </row>
     <row r="207">
@@ -9761,7 +10581,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr"/>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the duration of 9,192,631,770 periods of the radiation corresponding to the transition between the two hyperfine levels of the ground state of the cesium 133 atom.</t>
+        </is>
+      </c>
       <c r="J207" t="inlineStr"/>
     </row>
     <row r="208">
@@ -9805,7 +10629,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr"/>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the duration of 9,192,631,770 periods of the radiation corresponding to the transition between the two hyperfine levels of the ground state of the cesium 133 atom.</t>
+        </is>
+      </c>
       <c r="J208" t="inlineStr"/>
     </row>
     <row r="209">
@@ -9849,7 +10677,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr"/>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the duration of 9,192,631,770 periods of the radiation corresponding to the transition between the two hyperfine levels of the ground state of the cesium 133 atom.</t>
+        </is>
+      </c>
       <c r="J209" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -9897,7 +10729,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr"/>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the duration of 9,192,631,770 periods of the radiation corresponding to the transition between the two hyperfine levels of the ground state of the cesium 133 atom.</t>
+        </is>
+      </c>
       <c r="J210" t="inlineStr"/>
     </row>
     <row r="211">
@@ -9941,7 +10777,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr"/>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the duration of 9,192,631,770 periods of the radiation corresponding to the transition between the two hyperfine levels of the ground state of the cesium 133 atom.</t>
+        </is>
+      </c>
       <c r="J211" t="inlineStr"/>
     </row>
     <row r="212">
@@ -9985,7 +10825,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr"/>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that classifies Entities according to some shared, possibly arbitrary, characteristic.</t>
+        </is>
+      </c>
       <c r="J212" t="inlineStr"/>
     </row>
     <row r="213">
@@ -10029,7 +10873,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr"/>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that classifies Entities according to some shared, possibly arbitrary, characteristic.</t>
+        </is>
+      </c>
       <c r="J213" t="inlineStr"/>
     </row>
     <row r="214">
@@ -10073,7 +10921,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr"/>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that classifies Entities according to some shared, possibly arbitrary, characteristic.</t>
+        </is>
+      </c>
       <c r="J214" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -10121,7 +10973,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr"/>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that classifies Entities according to some shared, possibly arbitrary, characteristic.</t>
+        </is>
+      </c>
       <c r="J215" t="inlineStr"/>
     </row>
     <row r="216">
@@ -10165,7 +11021,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr"/>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that classifies Entities according to some shared, possibly arbitrary, characteristic.</t>
+        </is>
+      </c>
       <c r="J216" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -10213,7 +11073,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that classifies Entities according to some shared, possibly arbitrary, characteristic.</t>
+        </is>
+      </c>
       <c r="J217" t="inlineStr"/>
     </row>
     <row r="218">
@@ -10257,7 +11121,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that classifies Entities according to some shared, possibly arbitrary, characteristic.</t>
+        </is>
+      </c>
       <c r="J218" t="inlineStr"/>
     </row>
     <row r="219">
@@ -10301,7 +11169,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr"/>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that classifies Entities according to some shared, possibly arbitrary, characteristic.</t>
+        </is>
+      </c>
       <c r="J219" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -10349,7 +11221,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr"/>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that classifies Entities according to some shared, possibly arbitrary, characteristic.</t>
+        </is>
+      </c>
       <c r="J220" t="inlineStr"/>
     </row>
     <row r="221">
@@ -10393,7 +11269,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr"/>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that classifies Entities according to some shared, possibly arbitrary, characteristic.</t>
+        </is>
+      </c>
       <c r="J221" t="inlineStr"/>
     </row>
     <row r="222">
@@ -10437,7 +11317,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr"/>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that classifies Entities according to some shared, possibly arbitrary, characteristic.</t>
+        </is>
+      </c>
       <c r="J222" t="inlineStr"/>
     </row>
     <row r="223">
@@ -10481,7 +11365,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr"/>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that classifies Entities according to some shared, possibly arbitrary, characteristic.</t>
+        </is>
+      </c>
       <c r="J223" t="inlineStr"/>
     </row>
     <row r="224">
@@ -10525,7 +11413,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr"/>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that classifies Entities according to some shared, possibly arbitrary, characteristic.</t>
+        </is>
+      </c>
       <c r="J224" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -10573,7 +11465,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I225" t="inlineStr"/>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that classifies Entities according to some shared, possibly arbitrary, characteristic.</t>
+        </is>
+      </c>
       <c r="J225" t="inlineStr"/>
     </row>
     <row r="226">
@@ -10617,7 +11513,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr"/>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>A Measurement Information Content Entity that consists of a symbol that classifies Entities according to some shared, possibly arbitrary, characteristic.</t>
+        </is>
+      </c>
       <c r="J226" t="inlineStr"/>
     </row>
     <row r="227">
@@ -10661,7 +11561,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr"/>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>A Time of Day as specified according to the Julian Calendar using the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J227" t="inlineStr"/>
     </row>
     <row r="228">
@@ -10705,7 +11609,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr"/>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>A Time of Day as specified according to the Julian Calendar using the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J228" t="inlineStr"/>
     </row>
     <row r="229">
@@ -10749,7 +11657,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr"/>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>A Time of Day as specified according to the Julian Calendar using the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J229" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -10797,7 +11709,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr"/>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>A Time of Day as specified according to the Julian Calendar using the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J230" t="inlineStr"/>
     </row>
     <row r="231">
@@ -10841,7 +11757,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr"/>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>A Time of Day as specified according to the Julian Calendar using the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J231" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -10889,7 +11809,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr"/>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>A Time of Day as specified according to the Julian Calendar using the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J232" t="inlineStr"/>
     </row>
     <row r="233">
@@ -10933,7 +11857,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr"/>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>A Time of Day as specified according to the Julian Calendar using the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J233" t="inlineStr"/>
     </row>
     <row r="234">
@@ -10977,7 +11905,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr"/>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>A Time of Day as specified according to the Julian Calendar using the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J234" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -11025,7 +11957,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr"/>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>A Time of Day as specified according to the Julian Calendar using the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J235" t="inlineStr"/>
     </row>
     <row r="236">
@@ -11069,7 +12005,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr"/>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>A Time of Day as specified according to the Julian Calendar using the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J236" t="inlineStr"/>
     </row>
     <row r="237">
@@ -11113,7 +12053,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr"/>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>A Time of Day as specified according to the Julian Calendar using the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J237" t="inlineStr"/>
     </row>
     <row r="238">
@@ -11157,7 +12101,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr"/>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>A Time of Day as specified according to the Julian Calendar using the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J238" t="inlineStr"/>
     </row>
     <row r="239">
@@ -11201,7 +12149,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr"/>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>A Time of Day as specified according to the Julian Calendar using the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J239" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -11249,7 +12201,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr"/>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>A Time of Day as specified according to the Julian Calendar using the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J240" t="inlineStr"/>
     </row>
     <row r="241">
@@ -11293,7 +12249,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr"/>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>A Time of Day as specified according to the Julian Calendar using the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J241" t="inlineStr"/>
     </row>
     <row r="242">
@@ -11337,7 +12297,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr"/>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>A Temporal Interval Identifier that designates some Day.</t>
+        </is>
+      </c>
       <c r="J242" t="inlineStr"/>
     </row>
     <row r="243">
@@ -11381,7 +12345,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr"/>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>A Temporal Interval Identifier that designates some Day.</t>
+        </is>
+      </c>
       <c r="J243" t="inlineStr"/>
     </row>
     <row r="244">
@@ -11425,7 +12393,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I244" t="inlineStr"/>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>A Temporal Interval Identifier that designates some Day.</t>
+        </is>
+      </c>
       <c r="J244" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -11473,7 +12445,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr"/>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>A Temporal Interval Identifier that designates some Day.</t>
+        </is>
+      </c>
       <c r="J245" t="inlineStr"/>
     </row>
     <row r="246">
@@ -11517,7 +12493,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr"/>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>A Temporal Interval Identifier that designates some Day.</t>
+        </is>
+      </c>
       <c r="J246" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -11565,7 +12545,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr"/>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>A Temporal Interval Identifier that designates some Day.</t>
+        </is>
+      </c>
       <c r="J247" t="inlineStr"/>
     </row>
     <row r="248">
@@ -11609,7 +12593,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I248" t="inlineStr"/>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>A Temporal Interval Identifier that designates some Day.</t>
+        </is>
+      </c>
       <c r="J248" t="inlineStr"/>
     </row>
     <row r="249">
@@ -11653,7 +12641,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr"/>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>A Temporal Interval Identifier that designates some Day.</t>
+        </is>
+      </c>
       <c r="J249" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -11701,7 +12693,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr"/>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>A Temporal Interval Identifier that designates some Day.</t>
+        </is>
+      </c>
       <c r="J250" t="inlineStr"/>
     </row>
     <row r="251">
@@ -11745,7 +12741,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr"/>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>A Temporal Interval Identifier that designates some Day.</t>
+        </is>
+      </c>
       <c r="J251" t="inlineStr"/>
     </row>
     <row r="252">
@@ -11789,7 +12789,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr"/>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>A Temporal Interval Identifier that designates some Day.</t>
+        </is>
+      </c>
       <c r="J252" t="inlineStr"/>
     </row>
     <row r="253">
@@ -11833,7 +12837,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I253" t="inlineStr"/>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>A Temporal Interval Identifier that designates some Day.</t>
+        </is>
+      </c>
       <c r="J253" t="inlineStr"/>
     </row>
     <row r="254">
@@ -11877,7 +12885,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I254" t="inlineStr"/>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>A Temporal Interval Identifier that designates some Day.</t>
+        </is>
+      </c>
       <c r="J254" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -11925,7 +12937,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I255" t="inlineStr"/>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>A Temporal Interval Identifier that designates some Day.</t>
+        </is>
+      </c>
       <c r="J255" t="inlineStr"/>
     </row>
     <row r="256">
@@ -11969,7 +12985,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I256" t="inlineStr"/>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>A Temporal Interval Identifier that designates some Day.</t>
+        </is>
+      </c>
       <c r="J256" t="inlineStr"/>
     </row>
     <row r="257">
@@ -12013,7 +13033,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I257" t="inlineStr"/>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Minutes and spans at least one Minute.</t>
+        </is>
+      </c>
       <c r="J257" t="inlineStr"/>
     </row>
     <row r="258">
@@ -12057,7 +13081,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I258" t="inlineStr"/>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Minutes and spans at least one Minute.</t>
+        </is>
+      </c>
       <c r="J258" t="inlineStr"/>
     </row>
     <row r="259">
@@ -12101,7 +13129,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I259" t="inlineStr"/>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Minutes and spans at least one Minute.</t>
+        </is>
+      </c>
       <c r="J259" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -12149,7 +13181,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr"/>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Minutes and spans at least one Minute.</t>
+        </is>
+      </c>
       <c r="J260" t="inlineStr"/>
     </row>
     <row r="261">
@@ -12193,7 +13229,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I261" t="inlineStr"/>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Minutes and spans at least one Minute.</t>
+        </is>
+      </c>
       <c r="J261" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -12241,7 +13281,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I262" t="inlineStr"/>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Minutes and spans at least one Minute.</t>
+        </is>
+      </c>
       <c r="J262" t="inlineStr"/>
     </row>
     <row r="263">
@@ -12285,7 +13329,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I263" t="inlineStr"/>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Minutes and spans at least one Minute.</t>
+        </is>
+      </c>
       <c r="J263" t="inlineStr"/>
     </row>
     <row r="264">
@@ -12329,7 +13377,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr"/>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Minutes and spans at least one Minute.</t>
+        </is>
+      </c>
       <c r="J264" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -12377,7 +13429,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I265" t="inlineStr"/>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Minutes and spans at least one Minute.</t>
+        </is>
+      </c>
       <c r="J265" t="inlineStr"/>
     </row>
     <row r="266">
@@ -12421,7 +13477,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I266" t="inlineStr"/>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Minutes and spans at least one Minute.</t>
+        </is>
+      </c>
       <c r="J266" t="inlineStr"/>
     </row>
     <row r="267">
@@ -12465,7 +13525,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I267" t="inlineStr"/>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Minutes and spans at least one Minute.</t>
+        </is>
+      </c>
       <c r="J267" t="inlineStr"/>
     </row>
     <row r="268">
@@ -12509,7 +13573,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I268" t="inlineStr"/>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Minutes and spans at least one Minute.</t>
+        </is>
+      </c>
       <c r="J268" t="inlineStr"/>
     </row>
     <row r="269">
@@ -12553,7 +13621,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I269" t="inlineStr"/>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Minutes and spans at least one Minute.</t>
+        </is>
+      </c>
       <c r="J269" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -12601,7 +13673,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I270" t="inlineStr"/>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Minutes and spans at least one Minute.</t>
+        </is>
+      </c>
       <c r="J270" t="inlineStr"/>
     </row>
     <row r="271">
@@ -12645,7 +13721,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I271" t="inlineStr"/>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Minutes and spans at least one Minute.</t>
+        </is>
+      </c>
       <c r="J271" t="inlineStr"/>
     </row>
     <row r="272">
@@ -12689,7 +13769,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I272" t="inlineStr"/>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Temporal Region.</t>
+        </is>
+      </c>
       <c r="J272" t="inlineStr"/>
     </row>
     <row r="273">
@@ -12733,7 +13817,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I273" t="inlineStr"/>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Temporal Region.</t>
+        </is>
+      </c>
       <c r="J273" t="inlineStr"/>
     </row>
     <row r="274">
@@ -12777,7 +13865,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I274" t="inlineStr"/>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Temporal Region.</t>
+        </is>
+      </c>
       <c r="J274" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -12825,7 +13917,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I275" t="inlineStr"/>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Temporal Region.</t>
+        </is>
+      </c>
       <c r="J275" t="inlineStr"/>
     </row>
     <row r="276">
@@ -12869,7 +13965,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I276" t="inlineStr"/>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Temporal Region.</t>
+        </is>
+      </c>
       <c r="J276" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -12917,7 +14017,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I277" t="inlineStr"/>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Temporal Region.</t>
+        </is>
+      </c>
       <c r="J277" t="inlineStr"/>
     </row>
     <row r="278">
@@ -12961,7 +14065,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I278" t="inlineStr"/>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Temporal Region.</t>
+        </is>
+      </c>
       <c r="J278" t="inlineStr"/>
     </row>
     <row r="279">
@@ -13005,7 +14113,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I279" t="inlineStr"/>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Temporal Region.</t>
+        </is>
+      </c>
       <c r="J279" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -13053,7 +14165,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I280" t="inlineStr"/>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Temporal Region.</t>
+        </is>
+      </c>
       <c r="J280" t="inlineStr"/>
     </row>
     <row r="281">
@@ -13097,7 +14213,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I281" t="inlineStr"/>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Temporal Region.</t>
+        </is>
+      </c>
       <c r="J281" t="inlineStr"/>
     </row>
     <row r="282">
@@ -13141,7 +14261,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I282" t="inlineStr"/>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Temporal Region.</t>
+        </is>
+      </c>
       <c r="J282" t="inlineStr"/>
     </row>
     <row r="283">
@@ -13185,7 +14309,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I283" t="inlineStr"/>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Temporal Region.</t>
+        </is>
+      </c>
       <c r="J283" t="inlineStr"/>
     </row>
     <row r="284">
@@ -13229,7 +14357,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I284" t="inlineStr"/>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Temporal Region.</t>
+        </is>
+      </c>
       <c r="J284" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -13277,7 +14409,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I285" t="inlineStr"/>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Temporal Region.</t>
+        </is>
+      </c>
       <c r="J285" t="inlineStr"/>
     </row>
     <row r="286">
@@ -13321,7 +14457,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I286" t="inlineStr"/>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Temporal Region.</t>
+        </is>
+      </c>
       <c r="J286" t="inlineStr"/>
     </row>
     <row r="287">
@@ -13365,7 +14505,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I287" t="inlineStr"/>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>A Quality that concretizes some Information Content Entity.</t>
+        </is>
+      </c>
       <c r="J287" t="inlineStr"/>
     </row>
     <row r="288">
@@ -13409,7 +14553,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I288" t="inlineStr"/>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>A Quality that concretizes some Information Content Entity.</t>
+        </is>
+      </c>
       <c r="J288" t="inlineStr"/>
     </row>
     <row r="289">
@@ -13453,7 +14601,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I289" t="inlineStr"/>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>A Quality that concretizes some Information Content Entity.</t>
+        </is>
+      </c>
       <c r="J289" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -13501,7 +14653,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I290" t="inlineStr"/>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>A Quality that concretizes some Information Content Entity.</t>
+        </is>
+      </c>
       <c r="J290" t="inlineStr"/>
     </row>
     <row r="291">
@@ -13545,7 +14701,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I291" t="inlineStr"/>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>A Quality that concretizes some Information Content Entity.</t>
+        </is>
+      </c>
       <c r="J291" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -13593,7 +14753,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I292" t="inlineStr"/>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>A Quality that concretizes some Information Content Entity.</t>
+        </is>
+      </c>
       <c r="J292" t="inlineStr"/>
     </row>
     <row r="293">
@@ -13637,7 +14801,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I293" t="inlineStr"/>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>A Quality that concretizes some Information Content Entity.</t>
+        </is>
+      </c>
       <c r="J293" t="inlineStr"/>
     </row>
     <row r="294">
@@ -13681,7 +14849,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I294" t="inlineStr"/>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>A Quality that concretizes some Information Content Entity.</t>
+        </is>
+      </c>
       <c r="J294" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -13729,7 +14901,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I295" t="inlineStr"/>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>A Quality that concretizes some Information Content Entity.</t>
+        </is>
+      </c>
       <c r="J295" t="inlineStr"/>
     </row>
     <row r="296">
@@ -13773,7 +14949,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I296" t="inlineStr"/>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>A Quality that concretizes some Information Content Entity.</t>
+        </is>
+      </c>
       <c r="J296" t="inlineStr"/>
     </row>
     <row r="297">
@@ -13817,7 +14997,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I297" t="inlineStr"/>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>A Quality that concretizes some Information Content Entity.</t>
+        </is>
+      </c>
       <c r="J297" t="inlineStr"/>
     </row>
     <row r="298">
@@ -13861,7 +15045,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I298" t="inlineStr"/>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>A Quality that concretizes some Information Content Entity.</t>
+        </is>
+      </c>
       <c r="J298" t="inlineStr"/>
     </row>
     <row r="299">
@@ -13905,7 +15093,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I299" t="inlineStr"/>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>A Quality that concretizes some Information Content Entity.</t>
+        </is>
+      </c>
       <c r="J299" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -13953,7 +15145,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I300" t="inlineStr"/>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>A Quality that concretizes some Information Content Entity.</t>
+        </is>
+      </c>
       <c r="J300" t="inlineStr"/>
     </row>
     <row r="301">
@@ -13997,7 +15193,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I301" t="inlineStr"/>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>A Quality that concretizes some Information Content Entity.</t>
+        </is>
+      </c>
       <c r="J301" t="inlineStr"/>
     </row>
     <row r="302">
@@ -14041,7 +15241,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I302" t="inlineStr"/>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Minutes.</t>
+        </is>
+      </c>
       <c r="J302" t="inlineStr"/>
     </row>
     <row r="303">
@@ -14085,7 +15289,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I303" t="inlineStr"/>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Minutes.</t>
+        </is>
+      </c>
       <c r="J303" t="inlineStr"/>
     </row>
     <row r="304">
@@ -14129,7 +15337,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I304" t="inlineStr"/>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Minutes.</t>
+        </is>
+      </c>
       <c r="J304" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -14177,7 +15389,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I305" t="inlineStr"/>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Minutes.</t>
+        </is>
+      </c>
       <c r="J305" t="inlineStr"/>
     </row>
     <row r="306">
@@ -14221,7 +15437,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I306" t="inlineStr"/>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Minutes.</t>
+        </is>
+      </c>
       <c r="J306" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -14269,7 +15489,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I307" t="inlineStr"/>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Minutes.</t>
+        </is>
+      </c>
       <c r="J307" t="inlineStr"/>
     </row>
     <row r="308">
@@ -14313,7 +15537,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I308" t="inlineStr"/>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Minutes.</t>
+        </is>
+      </c>
       <c r="J308" t="inlineStr"/>
     </row>
     <row r="309">
@@ -14357,7 +15585,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I309" t="inlineStr"/>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Minutes.</t>
+        </is>
+      </c>
       <c r="J309" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -14405,7 +15637,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I310" t="inlineStr"/>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Minutes.</t>
+        </is>
+      </c>
       <c r="J310" t="inlineStr"/>
     </row>
     <row r="311">
@@ -14449,7 +15685,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I311" t="inlineStr"/>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Minutes.</t>
+        </is>
+      </c>
       <c r="J311" t="inlineStr"/>
     </row>
     <row r="312">
@@ -14493,7 +15733,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I312" t="inlineStr"/>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Minutes.</t>
+        </is>
+      </c>
       <c r="J312" t="inlineStr"/>
     </row>
     <row r="313">
@@ -14537,7 +15781,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I313" t="inlineStr"/>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Minutes.</t>
+        </is>
+      </c>
       <c r="J313" t="inlineStr"/>
     </row>
     <row r="314">
@@ -14581,7 +15829,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I314" t="inlineStr"/>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Minutes.</t>
+        </is>
+      </c>
       <c r="J314" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -14629,7 +15881,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I315" t="inlineStr"/>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Minutes.</t>
+        </is>
+      </c>
       <c r="J315" t="inlineStr"/>
     </row>
     <row r="316">
@@ -14673,7 +15929,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I316" t="inlineStr"/>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Minutes.</t>
+        </is>
+      </c>
       <c r="J316" t="inlineStr"/>
     </row>
     <row r="317">
@@ -14717,7 +15977,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I317" t="inlineStr"/>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Months and spans at least one Month.</t>
+        </is>
+      </c>
       <c r="J317" t="inlineStr"/>
     </row>
     <row r="318">
@@ -14761,7 +16025,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I318" t="inlineStr"/>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Months and spans at least one Month.</t>
+        </is>
+      </c>
       <c r="J318" t="inlineStr"/>
     </row>
     <row r="319">
@@ -14805,7 +16073,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I319" t="inlineStr"/>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Months and spans at least one Month.</t>
+        </is>
+      </c>
       <c r="J319" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -14853,7 +16125,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I320" t="inlineStr"/>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Months and spans at least one Month.</t>
+        </is>
+      </c>
       <c r="J320" t="inlineStr"/>
     </row>
     <row r="321">
@@ -14897,7 +16173,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I321" t="inlineStr"/>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Months and spans at least one Month.</t>
+        </is>
+      </c>
       <c r="J321" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -14945,7 +16225,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I322" t="inlineStr"/>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Months and spans at least one Month.</t>
+        </is>
+      </c>
       <c r="J322" t="inlineStr"/>
     </row>
     <row r="323">
@@ -14989,7 +16273,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I323" t="inlineStr"/>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Months and spans at least one Month.</t>
+        </is>
+      </c>
       <c r="J323" t="inlineStr"/>
     </row>
     <row r="324">
@@ -15033,7 +16321,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I324" t="inlineStr"/>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Months and spans at least one Month.</t>
+        </is>
+      </c>
       <c r="J324" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -15081,7 +16373,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I325" t="inlineStr"/>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Months and spans at least one Month.</t>
+        </is>
+      </c>
       <c r="J325" t="inlineStr"/>
     </row>
     <row r="326">
@@ -15125,7 +16421,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I326" t="inlineStr"/>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Months and spans at least one Month.</t>
+        </is>
+      </c>
       <c r="J326" t="inlineStr"/>
     </row>
     <row r="327">
@@ -15169,7 +16469,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I327" t="inlineStr"/>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Months and spans at least one Month.</t>
+        </is>
+      </c>
       <c r="J327" t="inlineStr"/>
     </row>
     <row r="328">
@@ -15213,7 +16517,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I328" t="inlineStr"/>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Months and spans at least one Month.</t>
+        </is>
+      </c>
       <c r="J328" t="inlineStr"/>
     </row>
     <row r="329">
@@ -15257,7 +16565,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I329" t="inlineStr"/>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Months and spans at least one Month.</t>
+        </is>
+      </c>
       <c r="J329" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -15305,7 +16617,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I330" t="inlineStr"/>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Months and spans at least one Month.</t>
+        </is>
+      </c>
       <c r="J330" t="inlineStr"/>
     </row>
     <row r="331">
@@ -15349,7 +16665,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I331" t="inlineStr"/>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Months and spans at least one Month.</t>
+        </is>
+      </c>
       <c r="J331" t="inlineStr"/>
     </row>
     <row r="332">
@@ -15393,7 +16713,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I332" t="inlineStr"/>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>A Generically Dependent Continuant that generically depends on some Information Bearing Entity and stands in relation of aboutness to some Entity.</t>
+        </is>
+      </c>
       <c r="J332" t="inlineStr"/>
     </row>
     <row r="333">
@@ -15437,7 +16761,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I333" t="inlineStr"/>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>A Generically Dependent Continuant that generically depends on some Information Bearing Entity and stands in relation of aboutness to some Entity.</t>
+        </is>
+      </c>
       <c r="J333" t="inlineStr"/>
     </row>
     <row r="334">
@@ -15481,7 +16809,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I334" t="inlineStr"/>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>A Generically Dependent Continuant that generically depends on some Information Bearing Entity and stands in relation of aboutness to some Entity.</t>
+        </is>
+      </c>
       <c r="J334" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -15529,7 +16861,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I335" t="inlineStr"/>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>A Generically Dependent Continuant that generically depends on some Information Bearing Entity and stands in relation of aboutness to some Entity.</t>
+        </is>
+      </c>
       <c r="J335" t="inlineStr"/>
     </row>
     <row r="336">
@@ -15573,7 +16909,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I336" t="inlineStr"/>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>A Generically Dependent Continuant that generically depends on some Information Bearing Entity and stands in relation of aboutness to some Entity.</t>
+        </is>
+      </c>
       <c r="J336" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -15621,7 +16961,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I337" t="inlineStr"/>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>A Generically Dependent Continuant that generically depends on some Information Bearing Entity and stands in relation of aboutness to some Entity.</t>
+        </is>
+      </c>
       <c r="J337" t="inlineStr"/>
     </row>
     <row r="338">
@@ -15665,7 +17009,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I338" t="inlineStr"/>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>A Generically Dependent Continuant that generically depends on some Information Bearing Entity and stands in relation of aboutness to some Entity.</t>
+        </is>
+      </c>
       <c r="J338" t="inlineStr"/>
     </row>
     <row r="339">
@@ -15709,7 +17057,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I339" t="inlineStr"/>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>A Generically Dependent Continuant that generically depends on some Information Bearing Entity and stands in relation of aboutness to some Entity.</t>
+        </is>
+      </c>
       <c r="J339" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -15757,7 +17109,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I340" t="inlineStr"/>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>A Generically Dependent Continuant that generically depends on some Information Bearing Entity and stands in relation of aboutness to some Entity.</t>
+        </is>
+      </c>
       <c r="J340" t="inlineStr"/>
     </row>
     <row r="341">
@@ -15801,7 +17157,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I341" t="inlineStr"/>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>A Generically Dependent Continuant that generically depends on some Information Bearing Entity and stands in relation of aboutness to some Entity.</t>
+        </is>
+      </c>
       <c r="J341" t="inlineStr"/>
     </row>
     <row r="342">
@@ -15845,7 +17205,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I342" t="inlineStr"/>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>A Generically Dependent Continuant that generically depends on some Information Bearing Entity and stands in relation of aboutness to some Entity.</t>
+        </is>
+      </c>
       <c r="J342" t="inlineStr"/>
     </row>
     <row r="343">
@@ -15889,7 +17253,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I343" t="inlineStr"/>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>A Generically Dependent Continuant that generically depends on some Information Bearing Entity and stands in relation of aboutness to some Entity.</t>
+        </is>
+      </c>
       <c r="J343" t="inlineStr"/>
     </row>
     <row r="344">
@@ -15933,7 +17301,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I344" t="inlineStr"/>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>A Generically Dependent Continuant that generically depends on some Information Bearing Entity and stands in relation of aboutness to some Entity.</t>
+        </is>
+      </c>
       <c r="J344" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -15981,7 +17353,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I345" t="inlineStr"/>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>A Generically Dependent Continuant that generically depends on some Information Bearing Entity and stands in relation of aboutness to some Entity.</t>
+        </is>
+      </c>
       <c r="J345" t="inlineStr"/>
     </row>
     <row r="346">
@@ -16025,7 +17401,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I346" t="inlineStr"/>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>A Generically Dependent Continuant that generically depends on some Information Bearing Entity and stands in relation of aboutness to some Entity.</t>
+        </is>
+      </c>
       <c r="J346" t="inlineStr"/>
     </row>
     <row r="347">
@@ -16069,7 +17449,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I347" t="inlineStr"/>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>A Prescriptive Information Content Entity that prescribes some aspect of the behavior of a participant in a Process given one or more operating conditions.</t>
+        </is>
+      </c>
       <c r="J347" t="inlineStr"/>
     </row>
     <row r="348">
@@ -16113,7 +17497,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I348" t="inlineStr"/>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>A Prescriptive Information Content Entity that prescribes some aspect of the behavior of a participant in a Process given one or more operating conditions.</t>
+        </is>
+      </c>
       <c r="J348" t="inlineStr"/>
     </row>
     <row r="349">
@@ -16157,7 +17545,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I349" t="inlineStr"/>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>A Prescriptive Information Content Entity that prescribes some aspect of the behavior of a participant in a Process given one or more operating conditions.</t>
+        </is>
+      </c>
       <c r="J349" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -16205,7 +17597,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I350" t="inlineStr"/>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>A Prescriptive Information Content Entity that prescribes some aspect of the behavior of a participant in a Process given one or more operating conditions.</t>
+        </is>
+      </c>
       <c r="J350" t="inlineStr"/>
     </row>
     <row r="351">
@@ -16249,7 +17645,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I351" t="inlineStr"/>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>A Prescriptive Information Content Entity that prescribes some aspect of the behavior of a participant in a Process given one or more operating conditions.</t>
+        </is>
+      </c>
       <c r="J351" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -16297,7 +17697,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I352" t="inlineStr"/>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>A Prescriptive Information Content Entity that prescribes some aspect of the behavior of a participant in a Process given one or more operating conditions.</t>
+        </is>
+      </c>
       <c r="J352" t="inlineStr"/>
     </row>
     <row r="353">
@@ -16341,7 +17745,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I353" t="inlineStr"/>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>A Prescriptive Information Content Entity that prescribes some aspect of the behavior of a participant in a Process given one or more operating conditions.</t>
+        </is>
+      </c>
       <c r="J353" t="inlineStr"/>
     </row>
     <row r="354">
@@ -16385,7 +17793,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I354" t="inlineStr"/>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>A Prescriptive Information Content Entity that prescribes some aspect of the behavior of a participant in a Process given one or more operating conditions.</t>
+        </is>
+      </c>
       <c r="J354" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -16433,7 +17845,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I355" t="inlineStr"/>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>A Prescriptive Information Content Entity that prescribes some aspect of the behavior of a participant in a Process given one or more operating conditions.</t>
+        </is>
+      </c>
       <c r="J355" t="inlineStr"/>
     </row>
     <row r="356">
@@ -16477,7 +17893,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I356" t="inlineStr"/>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>A Prescriptive Information Content Entity that prescribes some aspect of the behavior of a participant in a Process given one or more operating conditions.</t>
+        </is>
+      </c>
       <c r="J356" t="inlineStr"/>
     </row>
     <row r="357">
@@ -16521,7 +17941,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I357" t="inlineStr"/>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>A Prescriptive Information Content Entity that prescribes some aspect of the behavior of a participant in a Process given one or more operating conditions.</t>
+        </is>
+      </c>
       <c r="J357" t="inlineStr"/>
     </row>
     <row r="358">
@@ -16565,7 +17989,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I358" t="inlineStr"/>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>A Prescriptive Information Content Entity that prescribes some aspect of the behavior of a participant in a Process given one or more operating conditions.</t>
+        </is>
+      </c>
       <c r="J358" t="inlineStr"/>
     </row>
     <row r="359">
@@ -16609,7 +18037,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I359" t="inlineStr"/>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>A Prescriptive Information Content Entity that prescribes some aspect of the behavior of a participant in a Process given one or more operating conditions.</t>
+        </is>
+      </c>
       <c r="J359" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -16657,7 +18089,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I360" t="inlineStr"/>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>A Prescriptive Information Content Entity that prescribes some aspect of the behavior of a participant in a Process given one or more operating conditions.</t>
+        </is>
+      </c>
       <c r="J360" t="inlineStr"/>
     </row>
     <row r="361">
@@ -16701,7 +18137,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I361" t="inlineStr"/>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>A Prescriptive Information Content Entity that prescribes some aspect of the behavior of a participant in a Process given one or more operating conditions.</t>
+        </is>
+      </c>
       <c r="J361" t="inlineStr"/>
     </row>
     <row r="362">
@@ -16745,7 +18185,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I362" t="inlineStr"/>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Hours and spans at least one Hour.</t>
+        </is>
+      </c>
       <c r="J362" t="inlineStr"/>
     </row>
     <row r="363">
@@ -16789,7 +18233,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I363" t="inlineStr"/>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Hours and spans at least one Hour.</t>
+        </is>
+      </c>
       <c r="J363" t="inlineStr"/>
     </row>
     <row r="364">
@@ -16833,7 +18281,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I364" t="inlineStr"/>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Hours and spans at least one Hour.</t>
+        </is>
+      </c>
       <c r="J364" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -16881,7 +18333,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I365" t="inlineStr"/>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Hours and spans at least one Hour.</t>
+        </is>
+      </c>
       <c r="J365" t="inlineStr"/>
     </row>
     <row r="366">
@@ -16925,7 +18381,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I366" t="inlineStr"/>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Hours and spans at least one Hour.</t>
+        </is>
+      </c>
       <c r="J366" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -16973,7 +18433,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I367" t="inlineStr"/>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Hours and spans at least one Hour.</t>
+        </is>
+      </c>
       <c r="J367" t="inlineStr"/>
     </row>
     <row r="368">
@@ -17017,7 +18481,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I368" t="inlineStr"/>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Hours and spans at least one Hour.</t>
+        </is>
+      </c>
       <c r="J368" t="inlineStr"/>
     </row>
     <row r="369">
@@ -17061,7 +18529,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I369" t="inlineStr"/>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Hours and spans at least one Hour.</t>
+        </is>
+      </c>
       <c r="J369" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -17109,7 +18581,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I370" t="inlineStr"/>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Hours and spans at least one Hour.</t>
+        </is>
+      </c>
       <c r="J370" t="inlineStr"/>
     </row>
     <row r="371">
@@ -17153,7 +18629,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I371" t="inlineStr"/>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Hours and spans at least one Hour.</t>
+        </is>
+      </c>
       <c r="J371" t="inlineStr"/>
     </row>
     <row r="372">
@@ -17197,7 +18677,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I372" t="inlineStr"/>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Hours and spans at least one Hour.</t>
+        </is>
+      </c>
       <c r="J372" t="inlineStr"/>
     </row>
     <row r="373">
@@ -17241,7 +18725,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I373" t="inlineStr"/>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Hours and spans at least one Hour.</t>
+        </is>
+      </c>
       <c r="J373" t="inlineStr"/>
     </row>
     <row r="374">
@@ -17285,7 +18773,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I374" t="inlineStr"/>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Hours and spans at least one Hour.</t>
+        </is>
+      </c>
       <c r="J374" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -17333,7 +18825,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I375" t="inlineStr"/>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Hours and spans at least one Hour.</t>
+        </is>
+      </c>
       <c r="J375" t="inlineStr"/>
     </row>
     <row r="376">
@@ -17377,7 +18873,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I376" t="inlineStr"/>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Hours and spans at least one Hour.</t>
+        </is>
+      </c>
       <c r="J376" t="inlineStr"/>
     </row>
     <row r="377">
@@ -17421,7 +18921,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I377" t="inlineStr"/>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>A Descriptive Information Content Entity that describes the extent, dimensions, quantity, or quality of an Entity relative to some standard.</t>
+        </is>
+      </c>
       <c r="J377" t="inlineStr"/>
     </row>
     <row r="378">
@@ -17465,7 +18969,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I378" t="inlineStr"/>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>A Descriptive Information Content Entity that describes the extent, dimensions, quantity, or quality of an Entity relative to some standard.</t>
+        </is>
+      </c>
       <c r="J378" t="inlineStr"/>
     </row>
     <row r="379">
@@ -17509,7 +19017,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I379" t="inlineStr"/>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>A Descriptive Information Content Entity that describes the extent, dimensions, quantity, or quality of an Entity relative to some standard.</t>
+        </is>
+      </c>
       <c r="J379" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -17557,7 +19069,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I380" t="inlineStr"/>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>A Descriptive Information Content Entity that describes the extent, dimensions, quantity, or quality of an Entity relative to some standard.</t>
+        </is>
+      </c>
       <c r="J380" t="inlineStr"/>
     </row>
     <row r="381">
@@ -17601,7 +19117,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I381" t="inlineStr"/>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>A Descriptive Information Content Entity that describes the extent, dimensions, quantity, or quality of an Entity relative to some standard.</t>
+        </is>
+      </c>
       <c r="J381" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -17649,7 +19169,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I382" t="inlineStr"/>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>A Descriptive Information Content Entity that describes the extent, dimensions, quantity, or quality of an Entity relative to some standard.</t>
+        </is>
+      </c>
       <c r="J382" t="inlineStr"/>
     </row>
     <row r="383">
@@ -17693,7 +19217,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I383" t="inlineStr"/>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>A Descriptive Information Content Entity that describes the extent, dimensions, quantity, or quality of an Entity relative to some standard.</t>
+        </is>
+      </c>
       <c r="J383" t="inlineStr"/>
     </row>
     <row r="384">
@@ -17737,7 +19265,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I384" t="inlineStr"/>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>A Descriptive Information Content Entity that describes the extent, dimensions, quantity, or quality of an Entity relative to some standard.</t>
+        </is>
+      </c>
       <c r="J384" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -17785,7 +19317,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I385" t="inlineStr"/>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>A Descriptive Information Content Entity that describes the extent, dimensions, quantity, or quality of an Entity relative to some standard.</t>
+        </is>
+      </c>
       <c r="J385" t="inlineStr"/>
     </row>
     <row r="386">
@@ -17829,7 +19365,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I386" t="inlineStr"/>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>A Descriptive Information Content Entity that describes the extent, dimensions, quantity, or quality of an Entity relative to some standard.</t>
+        </is>
+      </c>
       <c r="J386" t="inlineStr"/>
     </row>
     <row r="387">
@@ -17873,7 +19413,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I387" t="inlineStr"/>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>A Descriptive Information Content Entity that describes the extent, dimensions, quantity, or quality of an Entity relative to some standard.</t>
+        </is>
+      </c>
       <c r="J387" t="inlineStr"/>
     </row>
     <row r="388">
@@ -17917,7 +19461,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I388" t="inlineStr"/>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>A Descriptive Information Content Entity that describes the extent, dimensions, quantity, or quality of an Entity relative to some standard.</t>
+        </is>
+      </c>
       <c r="J388" t="inlineStr"/>
     </row>
     <row r="389">
@@ -17961,7 +19509,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I389" t="inlineStr"/>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>A Descriptive Information Content Entity that describes the extent, dimensions, quantity, or quality of an Entity relative to some standard.</t>
+        </is>
+      </c>
       <c r="J389" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -18009,7 +19561,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I390" t="inlineStr"/>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>A Descriptive Information Content Entity that describes the extent, dimensions, quantity, or quality of an Entity relative to some standard.</t>
+        </is>
+      </c>
       <c r="J390" t="inlineStr"/>
     </row>
     <row r="391">
@@ -18053,7 +19609,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I391" t="inlineStr"/>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>A Descriptive Information Content Entity that describes the extent, dimensions, quantity, or quality of an Entity relative to some standard.</t>
+        </is>
+      </c>
       <c r="J391" t="inlineStr"/>
     </row>
     <row r="392">
@@ -18097,7 +19657,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I392" t="inlineStr"/>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Seconds and spans at least one Second.</t>
+        </is>
+      </c>
       <c r="J392" t="inlineStr"/>
     </row>
     <row r="393">
@@ -18141,7 +19705,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I393" t="inlineStr"/>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Seconds and spans at least one Second.</t>
+        </is>
+      </c>
       <c r="J393" t="inlineStr"/>
     </row>
     <row r="394">
@@ -18185,7 +19753,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I394" t="inlineStr"/>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Seconds and spans at least one Second.</t>
+        </is>
+      </c>
       <c r="J394" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -18233,7 +19805,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I395" t="inlineStr"/>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Seconds and spans at least one Second.</t>
+        </is>
+      </c>
       <c r="J395" t="inlineStr"/>
     </row>
     <row r="396">
@@ -18277,7 +19853,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I396" t="inlineStr"/>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Seconds and spans at least one Second.</t>
+        </is>
+      </c>
       <c r="J396" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -18325,7 +19905,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I397" t="inlineStr"/>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Seconds and spans at least one Second.</t>
+        </is>
+      </c>
       <c r="J397" t="inlineStr"/>
     </row>
     <row r="398">
@@ -18369,7 +19953,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I398" t="inlineStr"/>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Seconds and spans at least one Second.</t>
+        </is>
+      </c>
       <c r="J398" t="inlineStr"/>
     </row>
     <row r="399">
@@ -18413,7 +20001,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I399" t="inlineStr"/>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Seconds and spans at least one Second.</t>
+        </is>
+      </c>
       <c r="J399" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -18461,7 +20053,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I400" t="inlineStr"/>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Seconds and spans at least one Second.</t>
+        </is>
+      </c>
       <c r="J400" t="inlineStr"/>
     </row>
     <row r="401">
@@ -18505,7 +20101,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I401" t="inlineStr"/>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Seconds and spans at least one Second.</t>
+        </is>
+      </c>
       <c r="J401" t="inlineStr"/>
     </row>
     <row r="402">
@@ -18549,7 +20149,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I402" t="inlineStr"/>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Seconds and spans at least one Second.</t>
+        </is>
+      </c>
       <c r="J402" t="inlineStr"/>
     </row>
     <row r="403">
@@ -18593,7 +20197,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I403" t="inlineStr"/>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Seconds and spans at least one Second.</t>
+        </is>
+      </c>
       <c r="J403" t="inlineStr"/>
     </row>
     <row r="404">
@@ -18637,7 +20245,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I404" t="inlineStr"/>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Seconds and spans at least one Second.</t>
+        </is>
+      </c>
       <c r="J404" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -18685,7 +20297,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I405" t="inlineStr"/>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Seconds and spans at least one Second.</t>
+        </is>
+      </c>
       <c r="J405" t="inlineStr"/>
     </row>
     <row r="406">
@@ -18729,7 +20345,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I406" t="inlineStr"/>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Seconds and spans at least one Second.</t>
+        </is>
+      </c>
       <c r="J406" t="inlineStr"/>
     </row>
     <row r="407">
@@ -18773,7 +20393,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I407" t="inlineStr"/>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>A Temporal Instant that is part of a Day.</t>
+        </is>
+      </c>
       <c r="J407" t="inlineStr"/>
     </row>
     <row r="408">
@@ -18817,7 +20441,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I408" t="inlineStr"/>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>A Temporal Instant that is part of a Day.</t>
+        </is>
+      </c>
       <c r="J408" t="inlineStr"/>
     </row>
     <row r="409">
@@ -18861,7 +20489,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I409" t="inlineStr"/>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>A Temporal Instant that is part of a Day.</t>
+        </is>
+      </c>
       <c r="J409" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -18909,7 +20541,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I410" t="inlineStr"/>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>A Temporal Instant that is part of a Day.</t>
+        </is>
+      </c>
       <c r="J410" t="inlineStr"/>
     </row>
     <row r="411">
@@ -18953,7 +20589,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I411" t="inlineStr"/>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>A Temporal Instant that is part of a Day.</t>
+        </is>
+      </c>
       <c r="J411" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -19001,7 +20641,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I412" t="inlineStr"/>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>A Temporal Instant that is part of a Day.</t>
+        </is>
+      </c>
       <c r="J412" t="inlineStr"/>
     </row>
     <row r="413">
@@ -19045,7 +20689,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I413" t="inlineStr"/>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>A Temporal Instant that is part of a Day.</t>
+        </is>
+      </c>
       <c r="J413" t="inlineStr"/>
     </row>
     <row r="414">
@@ -19089,7 +20737,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I414" t="inlineStr"/>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>A Temporal Instant that is part of a Day.</t>
+        </is>
+      </c>
       <c r="J414" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -19137,7 +20789,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I415" t="inlineStr"/>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>A Temporal Instant that is part of a Day.</t>
+        </is>
+      </c>
       <c r="J415" t="inlineStr"/>
     </row>
     <row r="416">
@@ -19181,7 +20837,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I416" t="inlineStr"/>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>A Temporal Instant that is part of a Day.</t>
+        </is>
+      </c>
       <c r="J416" t="inlineStr"/>
     </row>
     <row r="417">
@@ -19225,7 +20885,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I417" t="inlineStr"/>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>A Temporal Instant that is part of a Day.</t>
+        </is>
+      </c>
       <c r="J417" t="inlineStr"/>
     </row>
     <row r="418">
@@ -19269,7 +20933,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I418" t="inlineStr"/>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>A Temporal Instant that is part of a Day.</t>
+        </is>
+      </c>
       <c r="J418" t="inlineStr"/>
     </row>
     <row r="419">
@@ -19313,7 +20981,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I419" t="inlineStr"/>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>A Temporal Instant that is part of a Day.</t>
+        </is>
+      </c>
       <c r="J419" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -19361,7 +21033,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I420" t="inlineStr"/>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>A Temporal Instant that is part of a Day.</t>
+        </is>
+      </c>
       <c r="J420" t="inlineStr"/>
     </row>
     <row r="421">
@@ -19405,7 +21081,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I421" t="inlineStr"/>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>A Temporal Instant that is part of a Day.</t>
+        </is>
+      </c>
       <c r="J421" t="inlineStr"/>
     </row>
     <row r="422">
@@ -19449,7 +21129,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I422" t="inlineStr"/>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Spatial Region.</t>
+        </is>
+      </c>
       <c r="J422" t="inlineStr"/>
     </row>
     <row r="423">
@@ -19493,7 +21177,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I423" t="inlineStr"/>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Spatial Region.</t>
+        </is>
+      </c>
       <c r="J423" t="inlineStr"/>
     </row>
     <row r="424">
@@ -19537,7 +21225,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I424" t="inlineStr"/>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Spatial Region.</t>
+        </is>
+      </c>
       <c r="J424" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -19585,7 +21277,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I425" t="inlineStr"/>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Spatial Region.</t>
+        </is>
+      </c>
       <c r="J425" t="inlineStr"/>
     </row>
     <row r="426">
@@ -19629,7 +21325,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I426" t="inlineStr"/>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Spatial Region.</t>
+        </is>
+      </c>
       <c r="J426" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -19677,7 +21377,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I427" t="inlineStr"/>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Spatial Region.</t>
+        </is>
+      </c>
       <c r="J427" t="inlineStr"/>
     </row>
     <row r="428">
@@ -19721,7 +21425,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I428" t="inlineStr"/>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Spatial Region.</t>
+        </is>
+      </c>
       <c r="J428" t="inlineStr"/>
     </row>
     <row r="429">
@@ -19765,7 +21473,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I429" t="inlineStr"/>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Spatial Region.</t>
+        </is>
+      </c>
       <c r="J429" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -19813,7 +21525,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I430" t="inlineStr"/>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Spatial Region.</t>
+        </is>
+      </c>
       <c r="J430" t="inlineStr"/>
     </row>
     <row r="431">
@@ -19857,7 +21573,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I431" t="inlineStr"/>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Spatial Region.</t>
+        </is>
+      </c>
       <c r="J431" t="inlineStr"/>
     </row>
     <row r="432">
@@ -19901,7 +21621,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I432" t="inlineStr"/>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Spatial Region.</t>
+        </is>
+      </c>
       <c r="J432" t="inlineStr"/>
     </row>
     <row r="433">
@@ -19945,7 +21669,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I433" t="inlineStr"/>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Spatial Region.</t>
+        </is>
+      </c>
       <c r="J433" t="inlineStr"/>
     </row>
     <row r="434">
@@ -19989,7 +21717,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I434" t="inlineStr"/>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Spatial Region.</t>
+        </is>
+      </c>
       <c r="J434" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -20037,7 +21769,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I435" t="inlineStr"/>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Spatial Region.</t>
+        </is>
+      </c>
       <c r="J435" t="inlineStr"/>
     </row>
     <row r="436">
@@ -20081,7 +21817,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I436" t="inlineStr"/>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>A Designative Information Content Entity that designates some Spatial Region.</t>
+        </is>
+      </c>
       <c r="J436" t="inlineStr"/>
     </row>
     <row r="437">
@@ -20125,7 +21865,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I437" t="inlineStr"/>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Instant.</t>
+        </is>
+      </c>
       <c r="J437" t="inlineStr"/>
     </row>
     <row r="438">
@@ -20169,7 +21913,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I438" t="inlineStr"/>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Instant.</t>
+        </is>
+      </c>
       <c r="J438" t="inlineStr"/>
     </row>
     <row r="439">
@@ -20213,7 +21961,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I439" t="inlineStr"/>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Instant.</t>
+        </is>
+      </c>
       <c r="J439" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -20261,7 +22013,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I440" t="inlineStr"/>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Instant.</t>
+        </is>
+      </c>
       <c r="J440" t="inlineStr"/>
     </row>
     <row r="441">
@@ -20305,7 +22061,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I441" t="inlineStr"/>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Instant.</t>
+        </is>
+      </c>
       <c r="J441" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -20353,7 +22113,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I442" t="inlineStr"/>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Instant.</t>
+        </is>
+      </c>
       <c r="J442" t="inlineStr"/>
     </row>
     <row r="443">
@@ -20397,7 +22161,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I443" t="inlineStr"/>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Instant.</t>
+        </is>
+      </c>
       <c r="J443" t="inlineStr"/>
     </row>
     <row r="444">
@@ -20441,7 +22209,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I444" t="inlineStr"/>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Instant.</t>
+        </is>
+      </c>
       <c r="J444" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -20489,7 +22261,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I445" t="inlineStr"/>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Instant.</t>
+        </is>
+      </c>
       <c r="J445" t="inlineStr"/>
     </row>
     <row r="446">
@@ -20533,7 +22309,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I446" t="inlineStr"/>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Instant.</t>
+        </is>
+      </c>
       <c r="J446" t="inlineStr"/>
     </row>
     <row r="447">
@@ -20577,7 +22357,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I447" t="inlineStr"/>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Instant.</t>
+        </is>
+      </c>
       <c r="J447" t="inlineStr"/>
     </row>
     <row r="448">
@@ -20621,7 +22405,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I448" t="inlineStr"/>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Instant.</t>
+        </is>
+      </c>
       <c r="J448" t="inlineStr"/>
     </row>
     <row r="449">
@@ -20665,7 +22453,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I449" t="inlineStr"/>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Instant.</t>
+        </is>
+      </c>
       <c r="J449" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -20713,7 +22505,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I450" t="inlineStr"/>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Instant.</t>
+        </is>
+      </c>
       <c r="J450" t="inlineStr"/>
     </row>
     <row r="451">
@@ -20757,7 +22553,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I451" t="inlineStr"/>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>A Temporal Region Identifier that designates some Temporal Instant.</t>
+        </is>
+      </c>
       <c r="J451" t="inlineStr"/>
     </row>
     <row r="452">
@@ -20801,7 +22601,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I452" t="inlineStr"/>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Days and spans at least one Day.</t>
+        </is>
+      </c>
       <c r="J452" t="inlineStr"/>
     </row>
     <row r="453">
@@ -20845,7 +22649,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I453" t="inlineStr"/>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Days and spans at least one Day.</t>
+        </is>
+      </c>
       <c r="J453" t="inlineStr"/>
     </row>
     <row r="454">
@@ -20889,7 +22697,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I454" t="inlineStr"/>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Days and spans at least one Day.</t>
+        </is>
+      </c>
       <c r="J454" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -20937,7 +22749,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I455" t="inlineStr"/>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Days and spans at least one Day.</t>
+        </is>
+      </c>
       <c r="J455" t="inlineStr"/>
     </row>
     <row r="456">
@@ -20981,7 +22797,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I456" t="inlineStr"/>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Days and spans at least one Day.</t>
+        </is>
+      </c>
       <c r="J456" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -21029,7 +22849,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I457" t="inlineStr"/>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Days and spans at least one Day.</t>
+        </is>
+      </c>
       <c r="J457" t="inlineStr"/>
     </row>
     <row r="458">
@@ -21073,7 +22897,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I458" t="inlineStr"/>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Days and spans at least one Day.</t>
+        </is>
+      </c>
       <c r="J458" t="inlineStr"/>
     </row>
     <row r="459">
@@ -21117,7 +22945,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I459" t="inlineStr"/>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Days and spans at least one Day.</t>
+        </is>
+      </c>
       <c r="J459" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -21165,7 +22997,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I460" t="inlineStr"/>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Days and spans at least one Day.</t>
+        </is>
+      </c>
       <c r="J460" t="inlineStr"/>
     </row>
     <row r="461">
@@ -21209,7 +23045,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I461" t="inlineStr"/>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Days and spans at least one Day.</t>
+        </is>
+      </c>
       <c r="J461" t="inlineStr"/>
     </row>
     <row r="462">
@@ -21253,7 +23093,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I462" t="inlineStr"/>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Days and spans at least one Day.</t>
+        </is>
+      </c>
       <c r="J462" t="inlineStr"/>
     </row>
     <row r="463">
@@ -21297,7 +23141,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I463" t="inlineStr"/>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Days and spans at least one Day.</t>
+        </is>
+      </c>
       <c r="J463" t="inlineStr"/>
     </row>
     <row r="464">
@@ -21341,7 +23189,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I464" t="inlineStr"/>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Days and spans at least one Day.</t>
+        </is>
+      </c>
       <c r="J464" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -21389,7 +23241,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I465" t="inlineStr"/>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Days and spans at least one Day.</t>
+        </is>
+      </c>
       <c r="J465" t="inlineStr"/>
     </row>
     <row r="466">
@@ -21433,7 +23289,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I466" t="inlineStr"/>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Days and spans at least one Day.</t>
+        </is>
+      </c>
       <c r="J466" t="inlineStr"/>
     </row>
     <row r="467">
@@ -21477,7 +23337,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I467" t="inlineStr"/>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>A Geospatial Region that is the location of an Independent Continuant (that is not a Spatial Region) or that environs some Process.</t>
+        </is>
+      </c>
       <c r="J467" t="inlineStr"/>
     </row>
     <row r="468">
@@ -21521,7 +23385,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I468" t="inlineStr"/>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>A Geospatial Region that is the location of an Independent Continuant (that is not a Spatial Region) or that environs some Process.</t>
+        </is>
+      </c>
       <c r="J468" t="inlineStr"/>
     </row>
     <row r="469">
@@ -21565,7 +23433,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I469" t="inlineStr"/>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>A Geospatial Region that is the location of an Independent Continuant (that is not a Spatial Region) or that environs some Process.</t>
+        </is>
+      </c>
       <c r="J469" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -21613,7 +23485,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I470" t="inlineStr"/>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>A Geospatial Region that is the location of an Independent Continuant (that is not a Spatial Region) or that environs some Process.</t>
+        </is>
+      </c>
       <c r="J470" t="inlineStr"/>
     </row>
     <row r="471">
@@ -21657,7 +23533,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I471" t="inlineStr"/>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>A Geospatial Region that is the location of an Independent Continuant (that is not a Spatial Region) or that environs some Process.</t>
+        </is>
+      </c>
       <c r="J471" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -21705,7 +23585,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I472" t="inlineStr"/>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>A Geospatial Region that is the location of an Independent Continuant (that is not a Spatial Region) or that environs some Process.</t>
+        </is>
+      </c>
       <c r="J472" t="inlineStr"/>
     </row>
     <row r="473">
@@ -21749,7 +23633,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I473" t="inlineStr"/>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>A Geospatial Region that is the location of an Independent Continuant (that is not a Spatial Region) or that environs some Process.</t>
+        </is>
+      </c>
       <c r="J473" t="inlineStr"/>
     </row>
     <row r="474">
@@ -21793,7 +23681,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I474" t="inlineStr"/>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>A Geospatial Region that is the location of an Independent Continuant (that is not a Spatial Region) or that environs some Process.</t>
+        </is>
+      </c>
       <c r="J474" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -21841,7 +23733,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I475" t="inlineStr"/>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>A Geospatial Region that is the location of an Independent Continuant (that is not a Spatial Region) or that environs some Process.</t>
+        </is>
+      </c>
       <c r="J475" t="inlineStr"/>
     </row>
     <row r="476">
@@ -21885,7 +23781,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I476" t="inlineStr"/>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>A Geospatial Region that is the location of an Independent Continuant (that is not a Spatial Region) or that environs some Process.</t>
+        </is>
+      </c>
       <c r="J476" t="inlineStr"/>
     </row>
     <row r="477">
@@ -21929,7 +23829,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I477" t="inlineStr"/>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>A Geospatial Region that is the location of an Independent Continuant (that is not a Spatial Region) or that environs some Process.</t>
+        </is>
+      </c>
       <c r="J477" t="inlineStr"/>
     </row>
     <row r="478">
@@ -21973,7 +23877,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I478" t="inlineStr"/>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>A Geospatial Region that is the location of an Independent Continuant (that is not a Spatial Region) or that environs some Process.</t>
+        </is>
+      </c>
       <c r="J478" t="inlineStr"/>
     </row>
     <row r="479">
@@ -22017,7 +23925,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I479" t="inlineStr"/>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>A Geospatial Region that is the location of an Independent Continuant (that is not a Spatial Region) or that environs some Process.</t>
+        </is>
+      </c>
       <c r="J479" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -22065,7 +23977,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I480" t="inlineStr"/>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>A Geospatial Region that is the location of an Independent Continuant (that is not a Spatial Region) or that environs some Process.</t>
+        </is>
+      </c>
       <c r="J480" t="inlineStr"/>
     </row>
     <row r="481">
@@ -22109,7 +24025,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I481" t="inlineStr"/>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>A Geospatial Region that is the location of an Independent Continuant (that is not a Spatial Region) or that environs some Process.</t>
+        </is>
+      </c>
       <c r="J481" t="inlineStr"/>
     </row>
     <row r="482">
@@ -22153,7 +24073,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I482" t="inlineStr"/>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>A Decimal Date Identifier that designates some Julian Day by using a number to indicate the sequential ordering of the Day since the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J482" t="inlineStr"/>
     </row>
     <row r="483">
@@ -22197,7 +24121,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I483" t="inlineStr"/>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>A Decimal Date Identifier that designates some Julian Day by using a number to indicate the sequential ordering of the Day since the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J483" t="inlineStr"/>
     </row>
     <row r="484">
@@ -22241,7 +24169,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I484" t="inlineStr"/>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>A Decimal Date Identifier that designates some Julian Day by using a number to indicate the sequential ordering of the Day since the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J484" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -22289,7 +24221,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I485" t="inlineStr"/>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>A Decimal Date Identifier that designates some Julian Day by using a number to indicate the sequential ordering of the Day since the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J485" t="inlineStr"/>
     </row>
     <row r="486">
@@ -22333,7 +24269,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I486" t="inlineStr"/>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>A Decimal Date Identifier that designates some Julian Day by using a number to indicate the sequential ordering of the Day since the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J486" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -22381,7 +24321,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I487" t="inlineStr"/>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>A Decimal Date Identifier that designates some Julian Day by using a number to indicate the sequential ordering of the Day since the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J487" t="inlineStr"/>
     </row>
     <row r="488">
@@ -22425,7 +24369,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I488" t="inlineStr"/>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>A Decimal Date Identifier that designates some Julian Day by using a number to indicate the sequential ordering of the Day since the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J488" t="inlineStr"/>
     </row>
     <row r="489">
@@ -22469,7 +24417,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I489" t="inlineStr"/>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>A Decimal Date Identifier that designates some Julian Day by using a number to indicate the sequential ordering of the Day since the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J489" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -22517,7 +24469,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I490" t="inlineStr"/>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>A Decimal Date Identifier that designates some Julian Day by using a number to indicate the sequential ordering of the Day since the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J490" t="inlineStr"/>
     </row>
     <row r="491">
@@ -22561,7 +24517,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I491" t="inlineStr"/>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>A Decimal Date Identifier that designates some Julian Day by using a number to indicate the sequential ordering of the Day since the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J491" t="inlineStr"/>
     </row>
     <row r="492">
@@ -22605,7 +24565,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I492" t="inlineStr"/>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>A Decimal Date Identifier that designates some Julian Day by using a number to indicate the sequential ordering of the Day since the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J492" t="inlineStr"/>
     </row>
     <row r="493">
@@ -22649,7 +24613,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I493" t="inlineStr"/>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>A Decimal Date Identifier that designates some Julian Day by using a number to indicate the sequential ordering of the Day since the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J493" t="inlineStr"/>
     </row>
     <row r="494">
@@ -22693,7 +24661,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I494" t="inlineStr"/>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>A Decimal Date Identifier that designates some Julian Day by using a number to indicate the sequential ordering of the Day since the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J494" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -22741,7 +24713,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I495" t="inlineStr"/>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>A Decimal Date Identifier that designates some Julian Day by using a number to indicate the sequential ordering of the Day since the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J495" t="inlineStr"/>
     </row>
     <row r="496">
@@ -22785,7 +24761,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I496" t="inlineStr"/>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>A Decimal Date Identifier that designates some Julian Day by using a number to indicate the sequential ordering of the Day since the Julian Date epoch.</t>
+        </is>
+      </c>
       <c r="J496" t="inlineStr"/>
     </row>
     <row r="497">
@@ -22829,7 +24809,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I497" t="inlineStr"/>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>A Three-Dimensional Spatial Region that encompasses the spatial region through which some Object travels.</t>
+        </is>
+      </c>
       <c r="J497" t="inlineStr"/>
     </row>
     <row r="498">
@@ -22873,7 +24857,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I498" t="inlineStr"/>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>A Three-Dimensional Spatial Region that encompasses the spatial region through which some Object travels.</t>
+        </is>
+      </c>
       <c r="J498" t="inlineStr"/>
     </row>
     <row r="499">
@@ -22917,7 +24905,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I499" t="inlineStr"/>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>A Three-Dimensional Spatial Region that encompasses the spatial region through which some Object travels.</t>
+        </is>
+      </c>
       <c r="J499" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -22965,7 +24957,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I500" t="inlineStr"/>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>A Three-Dimensional Spatial Region that encompasses the spatial region through which some Object travels.</t>
+        </is>
+      </c>
       <c r="J500" t="inlineStr"/>
     </row>
     <row r="501">
@@ -23009,7 +25005,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I501" t="inlineStr"/>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>A Three-Dimensional Spatial Region that encompasses the spatial region through which some Object travels.</t>
+        </is>
+      </c>
       <c r="J501" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -23057,7 +25057,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I502" t="inlineStr"/>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>A Three-Dimensional Spatial Region that encompasses the spatial region through which some Object travels.</t>
+        </is>
+      </c>
       <c r="J502" t="inlineStr"/>
     </row>
     <row r="503">
@@ -23101,7 +25105,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I503" t="inlineStr"/>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>A Three-Dimensional Spatial Region that encompasses the spatial region through which some Object travels.</t>
+        </is>
+      </c>
       <c r="J503" t="inlineStr"/>
     </row>
     <row r="504">
@@ -23145,7 +25153,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I504" t="inlineStr"/>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>A Three-Dimensional Spatial Region that encompasses the spatial region through which some Object travels.</t>
+        </is>
+      </c>
       <c r="J504" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -23193,7 +25205,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I505" t="inlineStr"/>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>A Three-Dimensional Spatial Region that encompasses the spatial region through which some Object travels.</t>
+        </is>
+      </c>
       <c r="J505" t="inlineStr"/>
     </row>
     <row r="506">
@@ -23237,7 +25253,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I506" t="inlineStr"/>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>A Three-Dimensional Spatial Region that encompasses the spatial region through which some Object travels.</t>
+        </is>
+      </c>
       <c r="J506" t="inlineStr"/>
     </row>
     <row r="507">
@@ -23281,7 +25301,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I507" t="inlineStr"/>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>A Three-Dimensional Spatial Region that encompasses the spatial region through which some Object travels.</t>
+        </is>
+      </c>
       <c r="J507" t="inlineStr"/>
     </row>
     <row r="508">
@@ -23325,7 +25349,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I508" t="inlineStr"/>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>A Three-Dimensional Spatial Region that encompasses the spatial region through which some Object travels.</t>
+        </is>
+      </c>
       <c r="J508" t="inlineStr"/>
     </row>
     <row r="509">
@@ -23369,7 +25397,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I509" t="inlineStr"/>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>A Three-Dimensional Spatial Region that encompasses the spatial region through which some Object travels.</t>
+        </is>
+      </c>
       <c r="J509" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -23417,7 +25449,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I510" t="inlineStr"/>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>A Three-Dimensional Spatial Region that encompasses the spatial region through which some Object travels.</t>
+        </is>
+      </c>
       <c r="J510" t="inlineStr"/>
     </row>
     <row r="511">
@@ -23461,7 +25497,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I511" t="inlineStr"/>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>A Three-Dimensional Spatial Region that encompasses the spatial region through which some Object travels.</t>
+        </is>
+      </c>
       <c r="J511" t="inlineStr"/>
     </row>
     <row r="512">
@@ -23505,7 +25545,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I512" t="inlineStr"/>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that prescribes some Entity.</t>
+        </is>
+      </c>
       <c r="J512" t="inlineStr"/>
     </row>
     <row r="513">
@@ -23549,7 +25593,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I513" t="inlineStr"/>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that prescribes some Entity.</t>
+        </is>
+      </c>
       <c r="J513" t="inlineStr"/>
     </row>
     <row r="514">
@@ -23593,7 +25641,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I514" t="inlineStr"/>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that prescribes some Entity.</t>
+        </is>
+      </c>
       <c r="J514" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -23641,7 +25693,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I515" t="inlineStr"/>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that prescribes some Entity.</t>
+        </is>
+      </c>
       <c r="J515" t="inlineStr"/>
     </row>
     <row r="516">
@@ -23685,7 +25741,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I516" t="inlineStr"/>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that prescribes some Entity.</t>
+        </is>
+      </c>
       <c r="J516" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -23733,7 +25793,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I517" t="inlineStr"/>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that prescribes some Entity.</t>
+        </is>
+      </c>
       <c r="J517" t="inlineStr"/>
     </row>
     <row r="518">
@@ -23777,7 +25841,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I518" t="inlineStr"/>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that prescribes some Entity.</t>
+        </is>
+      </c>
       <c r="J518" t="inlineStr"/>
     </row>
     <row r="519">
@@ -23821,7 +25889,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I519" t="inlineStr"/>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that prescribes some Entity.</t>
+        </is>
+      </c>
       <c r="J519" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -23869,7 +25941,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I520" t="inlineStr"/>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that prescribes some Entity.</t>
+        </is>
+      </c>
       <c r="J520" t="inlineStr"/>
     </row>
     <row r="521">
@@ -23913,7 +25989,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I521" t="inlineStr"/>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that prescribes some Entity.</t>
+        </is>
+      </c>
       <c r="J521" t="inlineStr"/>
     </row>
     <row r="522">
@@ -23957,7 +26037,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I522" t="inlineStr"/>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that prescribes some Entity.</t>
+        </is>
+      </c>
       <c r="J522" t="inlineStr"/>
     </row>
     <row r="523">
@@ -24001,7 +26085,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I523" t="inlineStr"/>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that prescribes some Entity.</t>
+        </is>
+      </c>
       <c r="J523" t="inlineStr"/>
     </row>
     <row r="524">
@@ -24045,7 +26133,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I524" t="inlineStr"/>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that prescribes some Entity.</t>
+        </is>
+      </c>
       <c r="J524" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -24093,7 +26185,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I525" t="inlineStr"/>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that prescribes some Entity.</t>
+        </is>
+      </c>
       <c r="J525" t="inlineStr"/>
     </row>
     <row r="526">
@@ -24137,7 +26233,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I526" t="inlineStr"/>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that prescribes some Entity.</t>
+        </is>
+      </c>
       <c r="J526" t="inlineStr"/>
     </row>
     <row r="527">
@@ -24181,7 +26281,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I527" t="inlineStr"/>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is based on the approximate length of time required for a Natural Satellite to complete one cycle of its rotational motion around its Primary Body.</t>
+        </is>
+      </c>
       <c r="J527" t="inlineStr"/>
     </row>
     <row r="528">
@@ -24225,7 +26329,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I528" t="inlineStr"/>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is based on the approximate length of time required for a Natural Satellite to complete one cycle of its rotational motion around its Primary Body.</t>
+        </is>
+      </c>
       <c r="J528" t="inlineStr"/>
     </row>
     <row r="529">
@@ -24269,7 +26377,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I529" t="inlineStr"/>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is based on the approximate length of time required for a Natural Satellite to complete one cycle of its rotational motion around its Primary Body.</t>
+        </is>
+      </c>
       <c r="J529" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -24317,7 +26429,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I530" t="inlineStr"/>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is based on the approximate length of time required for a Natural Satellite to complete one cycle of its rotational motion around its Primary Body.</t>
+        </is>
+      </c>
       <c r="J530" t="inlineStr"/>
     </row>
     <row r="531">
@@ -24361,7 +26477,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I531" t="inlineStr"/>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is based on the approximate length of time required for a Natural Satellite to complete one cycle of its rotational motion around its Primary Body.</t>
+        </is>
+      </c>
       <c r="J531" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -24409,7 +26529,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I532" t="inlineStr"/>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is based on the approximate length of time required for a Natural Satellite to complete one cycle of its rotational motion around its Primary Body.</t>
+        </is>
+      </c>
       <c r="J532" t="inlineStr"/>
     </row>
     <row r="533">
@@ -24453,7 +26577,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I533" t="inlineStr"/>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is based on the approximate length of time required for a Natural Satellite to complete one cycle of its rotational motion around its Primary Body.</t>
+        </is>
+      </c>
       <c r="J533" t="inlineStr"/>
     </row>
     <row r="534">
@@ -24497,7 +26625,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I534" t="inlineStr"/>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is based on the approximate length of time required for a Natural Satellite to complete one cycle of its rotational motion around its Primary Body.</t>
+        </is>
+      </c>
       <c r="J534" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -24545,7 +26677,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I535" t="inlineStr"/>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is based on the approximate length of time required for a Natural Satellite to complete one cycle of its rotational motion around its Primary Body.</t>
+        </is>
+      </c>
       <c r="J535" t="inlineStr"/>
     </row>
     <row r="536">
@@ -24589,7 +26725,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I536" t="inlineStr"/>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is based on the approximate length of time required for a Natural Satellite to complete one cycle of its rotational motion around its Primary Body.</t>
+        </is>
+      </c>
       <c r="J536" t="inlineStr"/>
     </row>
     <row r="537">
@@ -24633,7 +26773,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I537" t="inlineStr"/>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is based on the approximate length of time required for a Natural Satellite to complete one cycle of its rotational motion around its Primary Body.</t>
+        </is>
+      </c>
       <c r="J537" t="inlineStr"/>
     </row>
     <row r="538">
@@ -24677,7 +26821,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I538" t="inlineStr"/>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is based on the approximate length of time required for a Natural Satellite to complete one cycle of its rotational motion around its Primary Body.</t>
+        </is>
+      </c>
       <c r="J538" t="inlineStr"/>
     </row>
     <row r="539">
@@ -24721,7 +26869,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I539" t="inlineStr"/>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is based on the approximate length of time required for a Natural Satellite to complete one cycle of its rotational motion around its Primary Body.</t>
+        </is>
+      </c>
       <c r="J539" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -24769,7 +26921,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I540" t="inlineStr"/>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is based on the approximate length of time required for a Natural Satellite to complete one cycle of its rotational motion around its Primary Body.</t>
+        </is>
+      </c>
       <c r="J540" t="inlineStr"/>
     </row>
     <row r="541">
@@ -24813,7 +26969,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I541" t="inlineStr"/>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is based on the approximate length of time required for a Natural Satellite to complete one cycle of its rotational motion around its Primary Body.</t>
+        </is>
+      </c>
       <c r="J541" t="inlineStr"/>
     </row>
     <row r="542">
@@ -24857,7 +27017,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I542" t="inlineStr"/>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one rotation around its Rotational Axis as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J542" t="inlineStr"/>
     </row>
     <row r="543">
@@ -24901,7 +27065,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I543" t="inlineStr"/>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one rotation around its Rotational Axis as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J543" t="inlineStr"/>
     </row>
     <row r="544">
@@ -24945,7 +27113,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I544" t="inlineStr"/>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one rotation around its Rotational Axis as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J544" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -24993,7 +27165,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I545" t="inlineStr"/>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one rotation around its Rotational Axis as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J545" t="inlineStr"/>
     </row>
     <row r="546">
@@ -25037,7 +27213,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I546" t="inlineStr"/>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one rotation around its Rotational Axis as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J546" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -25085,7 +27265,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I547" t="inlineStr"/>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one rotation around its Rotational Axis as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J547" t="inlineStr"/>
     </row>
     <row r="548">
@@ -25129,7 +27313,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I548" t="inlineStr"/>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one rotation around its Rotational Axis as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J548" t="inlineStr"/>
     </row>
     <row r="549">
@@ -25173,7 +27361,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I549" t="inlineStr"/>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one rotation around its Rotational Axis as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J549" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -25221,7 +27413,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I550" t="inlineStr"/>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one rotation around its Rotational Axis as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J550" t="inlineStr"/>
     </row>
     <row r="551">
@@ -25265,7 +27461,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I551" t="inlineStr"/>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one rotation around its Rotational Axis as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J551" t="inlineStr"/>
     </row>
     <row r="552">
@@ -25309,7 +27509,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I552" t="inlineStr"/>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one rotation around its Rotational Axis as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J552" t="inlineStr"/>
     </row>
     <row r="553">
@@ -25353,7 +27557,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I553" t="inlineStr"/>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one rotation around its Rotational Axis as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J553" t="inlineStr"/>
     </row>
     <row r="554">
@@ -25397,7 +27605,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I554" t="inlineStr"/>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one rotation around its Rotational Axis as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J554" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -25445,7 +27657,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I555" t="inlineStr"/>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one rotation around its Rotational Axis as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J555" t="inlineStr"/>
     </row>
     <row r="556">
@@ -25489,7 +27705,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I556" t="inlineStr"/>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one rotation around its Rotational Axis as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
       <c r="J556" t="inlineStr"/>
     </row>
     <row r="557">
@@ -25533,7 +27753,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I557" t="inlineStr"/>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>An Object upon which an Information Content Entity generically depends.</t>
+        </is>
+      </c>
       <c r="J557" t="inlineStr"/>
     </row>
     <row r="558">
@@ -25577,7 +27801,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I558" t="inlineStr"/>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>An Object upon which an Information Content Entity generically depends.</t>
+        </is>
+      </c>
       <c r="J558" t="inlineStr"/>
     </row>
     <row r="559">
@@ -25621,7 +27849,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I559" t="inlineStr"/>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>An Object upon which an Information Content Entity generically depends.</t>
+        </is>
+      </c>
       <c r="J559" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -25669,7 +27901,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I560" t="inlineStr"/>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>An Object upon which an Information Content Entity generically depends.</t>
+        </is>
+      </c>
       <c r="J560" t="inlineStr"/>
     </row>
     <row r="561">
@@ -25713,7 +27949,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I561" t="inlineStr"/>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>An Object upon which an Information Content Entity generically depends.</t>
+        </is>
+      </c>
       <c r="J561" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -25761,7 +28001,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I562" t="inlineStr"/>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>An Object upon which an Information Content Entity generically depends.</t>
+        </is>
+      </c>
       <c r="J562" t="inlineStr"/>
     </row>
     <row r="563">
@@ -25805,7 +28049,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I563" t="inlineStr"/>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>An Object upon which an Information Content Entity generically depends.</t>
+        </is>
+      </c>
       <c r="J563" t="inlineStr"/>
     </row>
     <row r="564">
@@ -25849,7 +28097,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I564" t="inlineStr"/>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>An Object upon which an Information Content Entity generically depends.</t>
+        </is>
+      </c>
       <c r="J564" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -25897,7 +28149,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I565" t="inlineStr"/>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>An Object upon which an Information Content Entity generically depends.</t>
+        </is>
+      </c>
       <c r="J565" t="inlineStr"/>
     </row>
     <row r="566">
@@ -25941,7 +28197,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I566" t="inlineStr"/>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>An Object upon which an Information Content Entity generically depends.</t>
+        </is>
+      </c>
       <c r="J566" t="inlineStr"/>
     </row>
     <row r="567">
@@ -25985,7 +28245,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I567" t="inlineStr"/>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>An Object upon which an Information Content Entity generically depends.</t>
+        </is>
+      </c>
       <c r="J567" t="inlineStr"/>
     </row>
     <row r="568">
@@ -26029,7 +28293,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I568" t="inlineStr"/>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>An Object upon which an Information Content Entity generically depends.</t>
+        </is>
+      </c>
       <c r="J568" t="inlineStr"/>
     </row>
     <row r="569">
@@ -26073,7 +28341,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I569" t="inlineStr"/>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>An Object upon which an Information Content Entity generically depends.</t>
+        </is>
+      </c>
       <c r="J569" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -26121,7 +28393,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I570" t="inlineStr"/>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>An Object upon which an Information Content Entity generically depends.</t>
+        </is>
+      </c>
       <c r="J570" t="inlineStr"/>
     </row>
     <row r="571">
@@ -26165,7 +28441,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I571" t="inlineStr"/>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>An Object upon which an Information Content Entity generically depends.</t>
+        </is>
+      </c>
       <c r="J571" t="inlineStr"/>
     </row>
     <row r="572">
@@ -26209,7 +28489,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I572" t="inlineStr"/>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that represents some Entity.</t>
+        </is>
+      </c>
       <c r="J572" t="inlineStr"/>
     </row>
     <row r="573">
@@ -26253,7 +28537,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I573" t="inlineStr"/>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that represents some Entity.</t>
+        </is>
+      </c>
       <c r="J573" t="inlineStr"/>
     </row>
     <row r="574">
@@ -26297,7 +28585,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I574" t="inlineStr"/>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that represents some Entity.</t>
+        </is>
+      </c>
       <c r="J574" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -26345,7 +28637,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I575" t="inlineStr"/>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that represents some Entity.</t>
+        </is>
+      </c>
       <c r="J575" t="inlineStr"/>
     </row>
     <row r="576">
@@ -26389,7 +28685,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I576" t="inlineStr"/>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that represents some Entity.</t>
+        </is>
+      </c>
       <c r="J576" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -26437,7 +28737,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I577" t="inlineStr"/>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that represents some Entity.</t>
+        </is>
+      </c>
       <c r="J577" t="inlineStr"/>
     </row>
     <row r="578">
@@ -26481,7 +28785,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I578" t="inlineStr"/>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that represents some Entity.</t>
+        </is>
+      </c>
       <c r="J578" t="inlineStr"/>
     </row>
     <row r="579">
@@ -26525,7 +28833,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I579" t="inlineStr"/>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that represents some Entity.</t>
+        </is>
+      </c>
       <c r="J579" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -26573,7 +28885,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I580" t="inlineStr"/>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that represents some Entity.</t>
+        </is>
+      </c>
       <c r="J580" t="inlineStr"/>
     </row>
     <row r="581">
@@ -26617,7 +28933,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I581" t="inlineStr"/>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that represents some Entity.</t>
+        </is>
+      </c>
       <c r="J581" t="inlineStr"/>
     </row>
     <row r="582">
@@ -26661,7 +28981,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I582" t="inlineStr"/>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that represents some Entity.</t>
+        </is>
+      </c>
       <c r="J582" t="inlineStr"/>
     </row>
     <row r="583">
@@ -26705,7 +29029,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I583" t="inlineStr"/>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that represents some Entity.</t>
+        </is>
+      </c>
       <c r="J583" t="inlineStr"/>
     </row>
     <row r="584">
@@ -26749,7 +29077,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I584" t="inlineStr"/>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that represents some Entity.</t>
+        </is>
+      </c>
       <c r="J584" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -26797,7 +29129,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I585" t="inlineStr"/>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that represents some Entity.</t>
+        </is>
+      </c>
       <c r="J585" t="inlineStr"/>
     </row>
     <row r="586">
@@ -26841,7 +29177,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I586" t="inlineStr"/>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>An Information Content Entity that represents some Entity.</t>
+        </is>
+      </c>
       <c r="J586" t="inlineStr"/>
     </row>
     <row r="587">
@@ -26885,7 +29225,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I587" t="inlineStr"/>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Seconds.</t>
+        </is>
+      </c>
       <c r="J587" t="inlineStr"/>
     </row>
     <row r="588">
@@ -26929,7 +29273,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I588" t="inlineStr"/>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Seconds.</t>
+        </is>
+      </c>
       <c r="J588" t="inlineStr"/>
     </row>
     <row r="589">
@@ -26973,7 +29321,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I589" t="inlineStr"/>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Seconds.</t>
+        </is>
+      </c>
       <c r="J589" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -27021,7 +29373,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I590" t="inlineStr"/>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Seconds.</t>
+        </is>
+      </c>
       <c r="J590" t="inlineStr"/>
     </row>
     <row r="591">
@@ -27065,7 +29421,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I591" t="inlineStr"/>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Seconds.</t>
+        </is>
+      </c>
       <c r="J591" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -27113,7 +29473,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I592" t="inlineStr"/>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Seconds.</t>
+        </is>
+      </c>
       <c r="J592" t="inlineStr"/>
     </row>
     <row r="593">
@@ -27157,7 +29521,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I593" t="inlineStr"/>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Seconds.</t>
+        </is>
+      </c>
       <c r="J593" t="inlineStr"/>
     </row>
     <row r="594">
@@ -27201,7 +29569,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I594" t="inlineStr"/>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Seconds.</t>
+        </is>
+      </c>
       <c r="J594" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -27249,7 +29621,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I595" t="inlineStr"/>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Seconds.</t>
+        </is>
+      </c>
       <c r="J595" t="inlineStr"/>
     </row>
     <row r="596">
@@ -27293,7 +29669,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I596" t="inlineStr"/>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Seconds.</t>
+        </is>
+      </c>
       <c r="J596" t="inlineStr"/>
     </row>
     <row r="597">
@@ -27337,7 +29717,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I597" t="inlineStr"/>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Seconds.</t>
+        </is>
+      </c>
       <c r="J597" t="inlineStr"/>
     </row>
     <row r="598">
@@ -27381,7 +29765,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I598" t="inlineStr"/>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Seconds.</t>
+        </is>
+      </c>
       <c r="J598" t="inlineStr"/>
     </row>
     <row r="599">
@@ -27425,7 +29813,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I599" t="inlineStr"/>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Seconds.</t>
+        </is>
+      </c>
       <c r="J599" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -27473,7 +29865,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I600" t="inlineStr"/>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Seconds.</t>
+        </is>
+      </c>
       <c r="J600" t="inlineStr"/>
     </row>
     <row r="601">
@@ -27517,7 +29913,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I601" t="inlineStr"/>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Seconds.</t>
+        </is>
+      </c>
       <c r="J601" t="inlineStr"/>
     </row>
     <row r="602">
@@ -27561,7 +29961,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I602" t="inlineStr"/>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>A Zero-Dimensional Spatial Region that is an idealized point where an Object is or was located during some motion.</t>
+        </is>
+      </c>
       <c r="J602" t="inlineStr"/>
     </row>
     <row r="603">
@@ -27605,7 +30009,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I603" t="inlineStr"/>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>A Zero-Dimensional Spatial Region that is an idealized point where an Object is or was located during some motion.</t>
+        </is>
+      </c>
       <c r="J603" t="inlineStr"/>
     </row>
     <row r="604">
@@ -27649,7 +30057,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I604" t="inlineStr"/>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>A Zero-Dimensional Spatial Region that is an idealized point where an Object is or was located during some motion.</t>
+        </is>
+      </c>
       <c r="J604" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -27697,7 +30109,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I605" t="inlineStr"/>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>A Zero-Dimensional Spatial Region that is an idealized point where an Object is or was located during some motion.</t>
+        </is>
+      </c>
       <c r="J605" t="inlineStr"/>
     </row>
     <row r="606">
@@ -27741,7 +30157,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I606" t="inlineStr"/>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>A Zero-Dimensional Spatial Region that is an idealized point where an Object is or was located during some motion.</t>
+        </is>
+      </c>
       <c r="J606" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -27789,7 +30209,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I607" t="inlineStr"/>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>A Zero-Dimensional Spatial Region that is an idealized point where an Object is or was located during some motion.</t>
+        </is>
+      </c>
       <c r="J607" t="inlineStr"/>
     </row>
     <row r="608">
@@ -27833,7 +30257,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I608" t="inlineStr"/>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>A Zero-Dimensional Spatial Region that is an idealized point where an Object is or was located during some motion.</t>
+        </is>
+      </c>
       <c r="J608" t="inlineStr"/>
     </row>
     <row r="609">
@@ -27877,7 +30305,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I609" t="inlineStr"/>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>A Zero-Dimensional Spatial Region that is an idealized point where an Object is or was located during some motion.</t>
+        </is>
+      </c>
       <c r="J609" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -27925,7 +30357,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I610" t="inlineStr"/>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>A Zero-Dimensional Spatial Region that is an idealized point where an Object is or was located during some motion.</t>
+        </is>
+      </c>
       <c r="J610" t="inlineStr"/>
     </row>
     <row r="611">
@@ -27969,7 +30405,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I611" t="inlineStr"/>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>A Zero-Dimensional Spatial Region that is an idealized point where an Object is or was located during some motion.</t>
+        </is>
+      </c>
       <c r="J611" t="inlineStr"/>
     </row>
     <row r="612">
@@ -28013,7 +30453,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I612" t="inlineStr"/>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>A Zero-Dimensional Spatial Region that is an idealized point where an Object is or was located during some motion.</t>
+        </is>
+      </c>
       <c r="J612" t="inlineStr"/>
     </row>
     <row r="613">
@@ -28057,7 +30501,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I613" t="inlineStr"/>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>A Zero-Dimensional Spatial Region that is an idealized point where an Object is or was located during some motion.</t>
+        </is>
+      </c>
       <c r="J613" t="inlineStr"/>
     </row>
     <row r="614">
@@ -28101,7 +30549,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I614" t="inlineStr"/>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>A Zero-Dimensional Spatial Region that is an idealized point where an Object is or was located during some motion.</t>
+        </is>
+      </c>
       <c r="J614" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -28149,7 +30601,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I615" t="inlineStr"/>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>A Zero-Dimensional Spatial Region that is an idealized point where an Object is or was located during some motion.</t>
+        </is>
+      </c>
       <c r="J615" t="inlineStr"/>
     </row>
     <row r="616">
@@ -28193,7 +30649,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I616" t="inlineStr"/>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>A Zero-Dimensional Spatial Region that is an idealized point where an Object is or was located during some motion.</t>
+        </is>
+      </c>
       <c r="J616" t="inlineStr"/>
     </row>
     <row r="617">
@@ -28237,7 +30697,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I617" t="inlineStr"/>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>A Media Content Entity that is a part of some document content entity, and which  prescribes the eliciation of information to be written or selected within the document content entity.</t>
+        </is>
+      </c>
       <c r="J617" t="inlineStr"/>
     </row>
     <row r="618">
@@ -28281,7 +30745,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I618" t="inlineStr"/>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>A Media Content Entity that is a part of some document content entity, and which  prescribes the eliciation of information to be written or selected within the document content entity.</t>
+        </is>
+      </c>
       <c r="J618" t="inlineStr"/>
     </row>
     <row r="619">
@@ -28325,7 +30793,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I619" t="inlineStr"/>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>A Media Content Entity that is a part of some document content entity, and which  prescribes the eliciation of information to be written or selected within the document content entity.</t>
+        </is>
+      </c>
       <c r="J619" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -28373,7 +30845,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I620" t="inlineStr"/>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>A Media Content Entity that is a part of some document content entity, and which  prescribes the eliciation of information to be written or selected within the document content entity.</t>
+        </is>
+      </c>
       <c r="J620" t="inlineStr"/>
     </row>
     <row r="621">
@@ -28417,7 +30893,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I621" t="inlineStr"/>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>A Media Content Entity that is a part of some document content entity, and which  prescribes the eliciation of information to be written or selected within the document content entity.</t>
+        </is>
+      </c>
       <c r="J621" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -28465,7 +30945,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I622" t="inlineStr"/>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>A Media Content Entity that is a part of some document content entity, and which  prescribes the eliciation of information to be written or selected within the document content entity.</t>
+        </is>
+      </c>
       <c r="J622" t="inlineStr"/>
     </row>
     <row r="623">
@@ -28509,7 +30993,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I623" t="inlineStr"/>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>A Media Content Entity that is a part of some document content entity, and which  prescribes the eliciation of information to be written or selected within the document content entity.</t>
+        </is>
+      </c>
       <c r="J623" t="inlineStr"/>
     </row>
     <row r="624">
@@ -28553,7 +31041,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I624" t="inlineStr"/>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>A Media Content Entity that is a part of some document content entity, and which  prescribes the eliciation of information to be written or selected within the document content entity.</t>
+        </is>
+      </c>
       <c r="J624" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -28601,7 +31093,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I625" t="inlineStr"/>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>A Media Content Entity that is a part of some document content entity, and which  prescribes the eliciation of information to be written or selected within the document content entity.</t>
+        </is>
+      </c>
       <c r="J625" t="inlineStr"/>
     </row>
     <row r="626">
@@ -28645,7 +31141,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I626" t="inlineStr"/>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>A Media Content Entity that is a part of some document content entity, and which  prescribes the eliciation of information to be written or selected within the document content entity.</t>
+        </is>
+      </c>
       <c r="J626" t="inlineStr"/>
     </row>
     <row r="627">
@@ -28689,7 +31189,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I627" t="inlineStr"/>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>A Media Content Entity that is a part of some document content entity, and which  prescribes the eliciation of information to be written or selected within the document content entity.</t>
+        </is>
+      </c>
       <c r="J627" t="inlineStr"/>
     </row>
     <row r="628">
@@ -28733,7 +31237,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I628" t="inlineStr"/>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>A Media Content Entity that is a part of some document content entity, and which  prescribes the eliciation of information to be written or selected within the document content entity.</t>
+        </is>
+      </c>
       <c r="J628" t="inlineStr"/>
     </row>
     <row r="629">
@@ -28777,7 +31285,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I629" t="inlineStr"/>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>A Media Content Entity that is a part of some document content entity, and which  prescribes the eliciation of information to be written or selected within the document content entity.</t>
+        </is>
+      </c>
       <c r="J629" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -28825,7 +31337,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I630" t="inlineStr"/>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>A Media Content Entity that is a part of some document content entity, and which  prescribes the eliciation of information to be written or selected within the document content entity.</t>
+        </is>
+      </c>
       <c r="J630" t="inlineStr"/>
     </row>
     <row r="631">
@@ -28869,7 +31385,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I631" t="inlineStr"/>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>A Media Content Entity that is a part of some document content entity, and which  prescribes the eliciation of information to be written or selected within the document content entity.</t>
+        </is>
+      </c>
       <c r="J631" t="inlineStr"/>
     </row>
     <row r="632">
@@ -28913,7 +31433,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
         </is>
       </c>
-      <c r="I632" t="inlineStr"/>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to seven consecutive Days.</t>
+        </is>
+      </c>
       <c r="J632" t="inlineStr"/>
     </row>
     <row r="633">
@@ -28957,7 +31481,11 @@
           <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
         </is>
       </c>
-      <c r="I633" t="inlineStr"/>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to seven consecutive Days.</t>
+        </is>
+      </c>
       <c r="J633" t="inlineStr"/>
     </row>
     <row r="634">
@@ -29001,7 +31529,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
         </is>
       </c>
-      <c r="I634" t="inlineStr"/>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to seven consecutive Days.</t>
+        </is>
+      </c>
       <c r="J634" t="inlineStr">
         <is>
           <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
@@ -29049,7 +31581,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
         </is>
       </c>
-      <c r="I635" t="inlineStr"/>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to seven consecutive Days.</t>
+        </is>
+      </c>
       <c r="J635" t="inlineStr"/>
     </row>
     <row r="636">
@@ -29093,7 +31629,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
         </is>
       </c>
-      <c r="I636" t="inlineStr"/>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to seven consecutive Days.</t>
+        </is>
+      </c>
       <c r="J636" t="inlineStr">
         <is>
           <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
@@ -29141,7 +31681,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
         </is>
       </c>
-      <c r="I637" t="inlineStr"/>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to seven consecutive Days.</t>
+        </is>
+      </c>
       <c r="J637" t="inlineStr"/>
     </row>
     <row r="638">
@@ -29185,7 +31729,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
         </is>
       </c>
-      <c r="I638" t="inlineStr"/>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to seven consecutive Days.</t>
+        </is>
+      </c>
       <c r="J638" t="inlineStr"/>
     </row>
     <row r="639">
@@ -29229,7 +31777,11 @@
           <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
         </is>
       </c>
-      <c r="I639" t="inlineStr"/>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to seven consecutive Days.</t>
+        </is>
+      </c>
       <c r="J639" t="inlineStr">
         <is>
           <t>units for measuring human resources</t>
@@ -29277,7 +31829,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
         </is>
       </c>
-      <c r="I640" t="inlineStr"/>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to seven consecutive Days.</t>
+        </is>
+      </c>
       <c r="J640" t="inlineStr"/>
     </row>
     <row r="641">
@@ -29321,7 +31877,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
         </is>
       </c>
-      <c r="I641" t="inlineStr"/>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to seven consecutive Days.</t>
+        </is>
+      </c>
       <c r="J641" t="inlineStr"/>
     </row>
     <row r="642">
@@ -29365,7 +31925,11 @@
           <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
         </is>
       </c>
-      <c r="I642" t="inlineStr"/>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to seven consecutive Days.</t>
+        </is>
+      </c>
       <c r="J642" t="inlineStr"/>
     </row>
     <row r="643">
@@ -29409,7 +31973,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
         </is>
       </c>
-      <c r="I643" t="inlineStr"/>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to seven consecutive Days.</t>
+        </is>
+      </c>
       <c r="J643" t="inlineStr"/>
     </row>
     <row r="644">
@@ -29453,7 +32021,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
         </is>
       </c>
-      <c r="I644" t="inlineStr"/>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to seven consecutive Days.</t>
+        </is>
+      </c>
       <c r="J644" t="inlineStr">
         <is>
           <t>The class of units used to measure the properties of electricity and magnetism.</t>
@@ -29501,7 +32073,11 @@
           <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
         </is>
       </c>
-      <c r="I645" t="inlineStr"/>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to seven consecutive Days.</t>
+        </is>
+      </c>
       <c r="J645" t="inlineStr"/>
     </row>
     <row r="646">
@@ -29545,7 +32121,11 @@
           <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
         </is>
       </c>
-      <c r="I646" t="inlineStr"/>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to seven consecutive Days.</t>
+        </is>
+      </c>
       <c r="J646" t="inlineStr"/>
     </row>
   </sheetData>
